--- a/jogos_2026-04-12.xlsx
+++ b/jogos_2026-04-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI317"/>
+  <dimension ref="A1:BI315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.96</v>
+        <v>2.08</v>
       </c>
       <c r="Q97" t="n">
-        <v>4.04</v>
+        <v>3.81</v>
       </c>
       <c r="R97" t="n">
-        <v>2.19</v>
+        <v>3.36</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.48</v>
+        <v>3.66</v>
       </c>
       <c r="R110" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.66</v>
+        <v>3.48</v>
       </c>
       <c r="R111" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AF111" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24782,12 +24782,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24970,7 +24970,7 @@
         <v>0</v>
       </c>
       <c r="BI124" s="3" t="n">
-        <v>46124.4375</v>
+        <v>46124.44444444445</v>
       </c>
     </row>
     <row r="125">
@@ -24979,27 +24979,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25167,7 +25167,7 @@
         <v>0</v>
       </c>
       <c r="BI125" s="3" t="n">
-        <v>46124.4375</v>
+        <v>46124.45833333334</v>
       </c>
     </row>
     <row r="126">
@@ -25176,12 +25176,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25364,7 +25364,7 @@
         <v>0</v>
       </c>
       <c r="BI126" s="3" t="n">
-        <v>46124.44444444445</v>
+        <v>46124.45833333334</v>
       </c>
     </row>
     <row r="127">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29313,12 +29313,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29501,7 +29501,7 @@
         <v>0</v>
       </c>
       <c r="BI147" s="3" t="n">
-        <v>46124.45833333334</v>
+        <v>46124.46875</v>
       </c>
     </row>
     <row r="148">
@@ -29510,12 +29510,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29698,7 +29698,7 @@
         <v>0</v>
       </c>
       <c r="BI148" s="3" t="n">
-        <v>46124.45833333334</v>
+        <v>46124.46875</v>
       </c>
     </row>
     <row r="149">
@@ -29707,27 +29707,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29895,7 +29895,7 @@
         <v>0</v>
       </c>
       <c r="BI149" s="3" t="n">
-        <v>46124.46875</v>
+        <v>46124.47916666666</v>
       </c>
     </row>
     <row r="150">
@@ -29904,12 +29904,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30092,7 +30092,7 @@
         <v>0</v>
       </c>
       <c r="BI150" s="3" t="n">
-        <v>46124.46875</v>
+        <v>46124.47916666666</v>
       </c>
     </row>
     <row r="151">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31677,12 +31677,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31865,7 +31865,7 @@
         <v>0</v>
       </c>
       <c r="BI159" s="3" t="n">
-        <v>46124.47916666666</v>
+        <v>46124.48958333334</v>
       </c>
     </row>
     <row r="160">
@@ -31874,12 +31874,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32062,7 +32062,7 @@
         <v>0</v>
       </c>
       <c r="BI160" s="3" t="n">
-        <v>46124.47916666666</v>
+        <v>46124.48958333334</v>
       </c>
     </row>
     <row r="161">
@@ -32071,12 +32071,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32259,7 +32259,7 @@
         <v>0</v>
       </c>
       <c r="BI161" s="3" t="n">
-        <v>46124.48958333334</v>
+        <v>46124.5</v>
       </c>
     </row>
     <row r="162">
@@ -32268,12 +32268,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32456,7 +32456,7 @@
         <v>0</v>
       </c>
       <c r="BI162" s="3" t="n">
-        <v>46124.48958333334</v>
+        <v>46124.5</v>
       </c>
     </row>
     <row r="163">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,22 +37789,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,22 +37986,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,22 +38380,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40004,13 +40004,13 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q201" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R201" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S201" t="n">
         <v>0</v>
@@ -40153,22 +40153,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,22 +40350,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,22 +40547,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,22 +40744,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40936,27 +40936,27 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q206" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R206" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41034,10 +41034,10 @@
         <v>0</v>
       </c>
       <c r="AE206" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF206" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG206" t="n">
         <v>0</v>
@@ -41124,7 +41124,7 @@
         <v>0</v>
       </c>
       <c r="BI206" s="3" t="n">
-        <v>46124.5</v>
+        <v>46124.51041666666</v>
       </c>
     </row>
     <row r="207">
@@ -41133,12 +41133,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q207" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41321,7 +41321,7 @@
         <v>0</v>
       </c>
       <c r="BI207" s="3" t="n">
-        <v>46124.5</v>
+        <v>46124.51041666666</v>
       </c>
     </row>
     <row r="208">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>3.38</v>
+        <v>2.65</v>
       </c>
       <c r="Q208" t="n">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="R208" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q209" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41724,12 +41724,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41912,7 +41912,7 @@
         <v>0</v>
       </c>
       <c r="BI210" s="3" t="n">
-        <v>46124.51041666666</v>
+        <v>46124.52083333334</v>
       </c>
     </row>
     <row r="211">
@@ -41921,12 +41921,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>2.02</v>
+        <v>2.98</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.25</v>
+        <v>3.91</v>
       </c>
       <c r="R211" t="n">
-        <v>4.68</v>
+        <v>2.36</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,16 +42019,16 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF211" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG211" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH211" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI211" t="n">
         <v>0</v>
@@ -42109,7 +42109,7 @@
         <v>0</v>
       </c>
       <c r="BI211" s="3" t="n">
-        <v>46124.51041666666</v>
+        <v>46124.52083333334</v>
       </c>
     </row>
     <row r="212">
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q212" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42222,10 +42222,10 @@
         <v>0</v>
       </c>
       <c r="AG212" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH212" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q215" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -42813,10 +42813,10 @@
         <v>0</v>
       </c>
       <c r="AG215" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH215" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI215" t="n">
         <v>0</v>
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q216" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43010,10 +43010,10 @@
         <v>0</v>
       </c>
       <c r="AG216" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH216" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI216" t="n">
         <v>0</v>
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43694,12 +43694,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q220" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43882,7 +43882,7 @@
         <v>0</v>
       </c>
       <c r="BI220" s="3" t="n">
-        <v>46124.52083333334</v>
+        <v>46124.54166666666</v>
       </c>
     </row>
     <row r="221">
@@ -43891,12 +43891,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43940,7 +43940,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P221" t="n">
@@ -44079,7 +44079,7 @@
         <v>0</v>
       </c>
       <c r="BI221" s="3" t="n">
-        <v>46124.52083333334</v>
+        <v>46124.54166666666</v>
       </c>
     </row>
     <row r="222">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44338,13 +44338,13 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q223" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R223" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45122,7 +45122,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46846,27 +46846,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47034,7 +47034,7 @@
         <v>0</v>
       </c>
       <c r="BI236" s="3" t="n">
-        <v>46124.54166666666</v>
+        <v>46124.55208333334</v>
       </c>
     </row>
     <row r="237">
@@ -47043,12 +47043,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47231,7 +47231,7 @@
         <v>0</v>
       </c>
       <c r="BI237" s="3" t="n">
-        <v>46124.54166666666</v>
+        <v>46124.55208333334</v>
       </c>
     </row>
     <row r="238">
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47437,12 +47437,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47625,7 +47625,7 @@
         <v>0</v>
       </c>
       <c r="BI239" s="3" t="n">
-        <v>46124.55208333334</v>
+        <v>46124.5625</v>
       </c>
     </row>
     <row r="240">
@@ -47634,12 +47634,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47822,7 +47822,7 @@
         <v>0</v>
       </c>
       <c r="BI240" s="3" t="n">
-        <v>46124.55208333334</v>
+        <v>46124.5625</v>
       </c>
     </row>
     <row r="241">
@@ -47836,22 +47836,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,22 +48427,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49210,12 +49210,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,133 +49263,133 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q248" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R248" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S248" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T248" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U248" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="V248" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W248" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X248" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y248" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z248" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA248" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB248" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC248" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD248" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE248" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF248" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG248" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH248" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI248" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AJ248" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK248" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL248" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM248" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN248" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO248" t="n">
         <v>0</v>
       </c>
       <c r="AP248" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ248" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR248" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS248" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AU248" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV248" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AW248" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX248" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY248" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ248" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA248" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB248" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC248" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD248" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE248" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF248" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG248" t="n">
         <v>0</v>
@@ -49398,7 +49398,7 @@
         <v>0</v>
       </c>
       <c r="BI248" s="3" t="n">
-        <v>46124.5625</v>
+        <v>46124.58333333334</v>
       </c>
     </row>
     <row r="249">
@@ -49407,27 +49407,27 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49595,7 +49595,7 @@
         <v>0</v>
       </c>
       <c r="BI249" s="3" t="n">
-        <v>46124.5625</v>
+        <v>46124.58333333334</v>
       </c>
     </row>
     <row r="250">
@@ -49609,22 +49609,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,22 +49806,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -49854,133 +49854,133 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q251" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S251" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T251" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U251" t="n">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="V251" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W251" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X251" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y251" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z251" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA251" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB251" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC251" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD251" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE251" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF251" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG251" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AH251" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI251" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="AJ251" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK251" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL251" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AM251" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN251" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AO251" t="n">
         <v>0</v>
       </c>
       <c r="AP251" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ251" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR251" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS251" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AT251" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AU251" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV251" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AW251" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AX251" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY251" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ251" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BA251" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB251" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC251" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD251" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE251" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF251" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG251" t="n">
         <v>0</v>
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,22 +50397,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,22 +50594,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50983,12 +50983,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51171,7 +51171,7 @@
         <v>0</v>
       </c>
       <c r="BI257" s="3" t="n">
-        <v>46124.58333333334</v>
+        <v>46124.59375</v>
       </c>
     </row>
     <row r="258">
@@ -51180,12 +51180,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51368,7 +51368,7 @@
         <v>0</v>
       </c>
       <c r="BI258" s="3" t="n">
-        <v>46124.58333333334</v>
+        <v>46124.59375</v>
       </c>
     </row>
     <row r="259">
@@ -51377,12 +51377,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51430,13 +51430,13 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q259" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R259" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S259" t="n">
         <v>0</v>
@@ -51475,10 +51475,10 @@
         <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF259" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG259" t="n">
         <v>0</v>
@@ -51565,7 +51565,7 @@
         <v>0</v>
       </c>
       <c r="BI259" s="3" t="n">
-        <v>46124.59375</v>
+        <v>46124.60416666666</v>
       </c>
     </row>
     <row r="260">
@@ -51574,27 +51574,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51762,7 +51762,7 @@
         <v>0</v>
       </c>
       <c r="BI260" s="3" t="n">
-        <v>46124.59375</v>
+        <v>46124.60416666666</v>
       </c>
     </row>
     <row r="261">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,133 +51824,133 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q261" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R261" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S261" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T261" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U261" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V261" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W261" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X261" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y261" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z261" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA261" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB261" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC261" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD261" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE261" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF261" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG261" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH261" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI261" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ261" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK261" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL261" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM261" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN261" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO261" t="n">
         <v>0</v>
       </c>
       <c r="AP261" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ261" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR261" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS261" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AU261" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AV261" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW261" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX261" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY261" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ261" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA261" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB261" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC261" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BD261" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE261" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF261" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG261" t="n">
         <v>0</v>
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52165,12 +52165,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52218,133 +52218,133 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>2.99</v>
+        <v>2.1</v>
       </c>
       <c r="Q263" t="n">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="R263" t="n">
-        <v>2.15</v>
+        <v>3.47</v>
       </c>
       <c r="S263" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T263" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U263" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V263" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W263" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X263" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Y263" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z263" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB263" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC263" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD263" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE263" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF263" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AG263" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH263" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI263" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ263" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK263" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL263" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM263" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN263" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO263" t="n">
         <v>0</v>
       </c>
       <c r="AP263" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ263" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR263" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS263" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AT263" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AU263" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AV263" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW263" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX263" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY263" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ263" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA263" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BB263" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC263" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BD263" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE263" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BF263" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG263" t="n">
         <v>0</v>
@@ -52353,7 +52353,7 @@
         <v>0</v>
       </c>
       <c r="BI263" s="3" t="n">
-        <v>46124.60416666666</v>
+        <v>46124.625</v>
       </c>
     </row>
     <row r="264">
@@ -52362,12 +52362,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52415,13 +52415,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q264" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -52460,10 +52460,10 @@
         <v>0</v>
       </c>
       <c r="AE264" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF264" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG264" t="n">
         <v>0</v>
@@ -52550,7 +52550,7 @@
         <v>0</v>
       </c>
       <c r="BI264" s="3" t="n">
-        <v>46124.60416666666</v>
+        <v>46124.625</v>
       </c>
     </row>
     <row r="265">
@@ -52756,12 +52756,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52944,7 +52944,7 @@
         <v>0</v>
       </c>
       <c r="BI266" s="3" t="n">
-        <v>46124.625</v>
+        <v>46124.64583333334</v>
       </c>
     </row>
     <row r="267">
@@ -52953,27 +52953,27 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53141,7 +53141,7 @@
         <v>0</v>
       </c>
       <c r="BI267" s="3" t="n">
-        <v>46124.625</v>
+        <v>46124.64583333334</v>
       </c>
     </row>
     <row r="268">
@@ -53155,22 +53155,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,22 +53352,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53794,13 +53794,13 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q271" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R271" t="n">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="S271" t="n">
         <v>0</v>
@@ -53839,10 +53839,10 @@
         <v>0</v>
       </c>
       <c r="AE271" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF271" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG271" t="n">
         <v>0</v>
@@ -53929,7 +53929,7 @@
         <v>0</v>
       </c>
       <c r="BI271" s="3" t="n">
-        <v>46124.64583333334</v>
+        <v>46124.65625</v>
       </c>
     </row>
     <row r="272">
@@ -53938,27 +53938,27 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q272" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R272" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54036,10 +54036,10 @@
         <v>0</v>
       </c>
       <c r="AE272" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF272" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG272" t="n">
         <v>0</v>
@@ -54126,7 +54126,7 @@
         <v>0</v>
       </c>
       <c r="BI272" s="3" t="n">
-        <v>46124.64583333334</v>
+        <v>46124.65625</v>
       </c>
     </row>
     <row r="273">
@@ -54135,12 +54135,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -54150,12 +54150,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q273" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>5.43</v>
+        <v>0</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54233,10 +54233,10 @@
         <v>0</v>
       </c>
       <c r="AE273" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF273" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG273" t="n">
         <v>0</v>
@@ -54323,7 +54323,7 @@
         <v>0</v>
       </c>
       <c r="BI273" s="3" t="n">
-        <v>46124.65625</v>
+        <v>46124.66666666666</v>
       </c>
     </row>
     <row r="274">
@@ -54332,27 +54332,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54385,13 +54385,13 @@
         </is>
       </c>
       <c r="P274" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q274" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R274" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S274" t="n">
         <v>0</v>
@@ -54430,10 +54430,10 @@
         <v>0</v>
       </c>
       <c r="AE274" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF274" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG274" t="n">
         <v>0</v>
@@ -54520,7 +54520,7 @@
         <v>0</v>
       </c>
       <c r="BI274" s="3" t="n">
-        <v>46124.65625</v>
+        <v>46124.66666666666</v>
       </c>
     </row>
     <row r="275">
@@ -54534,7 +54534,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -54544,12 +54544,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,22 +54731,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54928,22 +54928,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55173,13 +55173,13 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q278" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R278" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="S278" t="n">
         <v>0</v>
@@ -55317,27 +55317,27 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55370,13 +55370,13 @@
         </is>
       </c>
       <c r="P279" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q279" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R279" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="S279" t="n">
         <v>0</v>
@@ -55505,7 +55505,7 @@
         <v>0</v>
       </c>
       <c r="BI279" s="3" t="n">
-        <v>46124.66666666666</v>
+        <v>46124.6875</v>
       </c>
     </row>
     <row r="280">
@@ -55514,27 +55514,27 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55702,7 +55702,7 @@
         <v>0</v>
       </c>
       <c r="BI280" s="3" t="n">
-        <v>46124.66666666666</v>
+        <v>46124.6875</v>
       </c>
     </row>
     <row r="281">
@@ -55711,12 +55711,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55899,7 +55899,7 @@
         <v>0</v>
       </c>
       <c r="BI281" s="3" t="n">
-        <v>46124.6875</v>
+        <v>46124.70833333334</v>
       </c>
     </row>
     <row r="282">
@@ -55908,27 +55908,27 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -56096,7 +56096,7 @@
         <v>0</v>
       </c>
       <c r="BI282" s="3" t="n">
-        <v>46124.6875</v>
+        <v>46124.70833333334</v>
       </c>
     </row>
     <row r="283">
@@ -56302,27 +56302,27 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56490,7 +56490,7 @@
         <v>0</v>
       </c>
       <c r="BI284" s="3" t="n">
-        <v>46124.70833333334</v>
+        <v>46124.72916666666</v>
       </c>
     </row>
     <row r="285">
@@ -56499,27 +56499,27 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56687,7 +56687,7 @@
         <v>0</v>
       </c>
       <c r="BI285" s="3" t="n">
-        <v>46124.70833333334</v>
+        <v>46124.72916666666</v>
       </c>
     </row>
     <row r="286">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56908,12 +56908,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57686,22 +57686,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57878,12 +57878,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -58066,7 +58066,7 @@
         <v>0</v>
       </c>
       <c r="BI292" s="3" t="n">
-        <v>46124.72916666666</v>
+        <v>46124.75</v>
       </c>
     </row>
     <row r="293">
@@ -58075,27 +58075,27 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58263,7 +58263,7 @@
         <v>0</v>
       </c>
       <c r="BI293" s="3" t="n">
-        <v>46124.72916666666</v>
+        <v>46124.75</v>
       </c>
     </row>
     <row r="294">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58474,7 +58474,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58522,13 +58522,13 @@
         </is>
       </c>
       <c r="P295" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q295" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R295" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S295" t="n">
         <v>0</v>
@@ -58666,12 +58666,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58719,13 +58719,13 @@
         </is>
       </c>
       <c r="P296" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q296" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R296" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S296" t="n">
         <v>0</v>
@@ -58854,7 +58854,7 @@
         <v>0</v>
       </c>
       <c r="BI296" s="3" t="n">
-        <v>46124.75</v>
+        <v>46124.77083333334</v>
       </c>
     </row>
     <row r="297">
@@ -58863,12 +58863,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -58916,13 +58916,13 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q297" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R297" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="S297" t="n">
         <v>0</v>
@@ -58961,10 +58961,10 @@
         <v>0</v>
       </c>
       <c r="AE297" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF297" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG297" t="n">
         <v>0</v>
@@ -59051,7 +59051,7 @@
         <v>0</v>
       </c>
       <c r="BI297" s="3" t="n">
-        <v>46124.75</v>
+        <v>46124.77083333334</v>
       </c>
     </row>
     <row r="298">
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59454,12 +59454,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59642,7 +59642,7 @@
         <v>0</v>
       </c>
       <c r="BI300" s="3" t="n">
-        <v>46124.77083333334</v>
+        <v>46124.83333333334</v>
       </c>
     </row>
     <row r="301">
@@ -59651,12 +59651,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59704,13 +59704,13 @@
         </is>
       </c>
       <c r="P301" t="n">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="Q301" t="n">
-        <v>3.79</v>
+        <v>4.73</v>
       </c>
       <c r="R301" t="n">
-        <v>4.63</v>
+        <v>5.61</v>
       </c>
       <c r="S301" t="n">
         <v>0</v>
@@ -59749,16 +59749,16 @@
         <v>0</v>
       </c>
       <c r="AE301" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF301" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG301" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH301" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI301" t="n">
         <v>0</v>
@@ -59839,7 +59839,7 @@
         <v>0</v>
       </c>
       <c r="BI301" s="3" t="n">
-        <v>46124.77083333334</v>
+        <v>46124.83333333334</v>
       </c>
     </row>
     <row r="302">
@@ -59853,7 +59853,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -60050,7 +60050,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60247,7 +60247,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60439,12 +60439,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60492,13 +60492,13 @@
         </is>
       </c>
       <c r="P305" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q305" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="R305" t="n">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="S305" t="n">
         <v>0</v>
@@ -60543,10 +60543,10 @@
         <v>0</v>
       </c>
       <c r="AG305" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH305" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI305" t="n">
         <v>0</v>
@@ -60627,7 +60627,7 @@
         <v>0</v>
       </c>
       <c r="BI305" s="3" t="n">
-        <v>46124.83333333334</v>
+        <v>46124.84027777778</v>
       </c>
     </row>
     <row r="306">
@@ -60636,12 +60636,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60824,7 +60824,7 @@
         <v>0</v>
       </c>
       <c r="BI306" s="3" t="n">
-        <v>46124.83333333334</v>
+        <v>46124.85416666666</v>
       </c>
     </row>
     <row r="307">
@@ -60833,12 +60833,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61021,7 +61021,7 @@
         <v>0</v>
       </c>
       <c r="BI307" s="3" t="n">
-        <v>46124.84027777778</v>
+        <v>46124.875</v>
       </c>
     </row>
     <row r="308">
@@ -61030,12 +61030,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61218,7 +61218,7 @@
         <v>0</v>
       </c>
       <c r="BI308" s="3" t="n">
-        <v>46124.85416666666</v>
+        <v>46124.875</v>
       </c>
     </row>
     <row r="309">
@@ -61232,7 +61232,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61429,7 +61429,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61626,7 +61626,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61823,7 +61823,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -61833,12 +61833,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -62015,12 +62015,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -62030,12 +62030,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -62203,7 +62203,7 @@
         <v>0</v>
       </c>
       <c r="BI313" s="3" t="n">
-        <v>46124.875</v>
+        <v>46124.89583333334</v>
       </c>
     </row>
     <row r="314">
@@ -62212,12 +62212,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -62227,12 +62227,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -62265,13 +62265,13 @@
         </is>
       </c>
       <c r="P314" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q314" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R314" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S314" t="n">
         <v>0</v>
@@ -62310,10 +62310,10 @@
         <v>0</v>
       </c>
       <c r="AE314" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG314" t="n">
         <v>0</v>
@@ -62400,7 +62400,7 @@
         <v>0</v>
       </c>
       <c r="BI314" s="3" t="n">
-        <v>46124.875</v>
+        <v>46124.91666666666</v>
       </c>
     </row>
     <row r="315">
@@ -62409,7 +62409,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -62424,12 +62424,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -62597,400 +62597,6 @@
         <v>0</v>
       </c>
       <c r="BI315" s="3" t="n">
-        <v>46124.89583333334</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="n">
-        <v>46124</v>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="G316" t="n">
-        <v>0</v>
-      </c>
-      <c r="H316" t="n">
-        <v>0</v>
-      </c>
-      <c r="I316" t="n">
-        <v>0</v>
-      </c>
-      <c r="J316" t="n">
-        <v>0</v>
-      </c>
-      <c r="K316" t="n">
-        <v>0</v>
-      </c>
-      <c r="L316" t="n">
-        <v>0</v>
-      </c>
-      <c r="M316" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N316" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O316" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P316" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q316" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="R316" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="S316" t="n">
-        <v>0</v>
-      </c>
-      <c r="T316" t="n">
-        <v>0</v>
-      </c>
-      <c r="U316" t="n">
-        <v>0</v>
-      </c>
-      <c r="V316" t="n">
-        <v>0</v>
-      </c>
-      <c r="W316" t="n">
-        <v>0</v>
-      </c>
-      <c r="X316" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y316" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE316" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF316" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY316" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ316" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA316" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB316" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC316" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD316" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE316" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF316" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG316" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH316" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI316" s="3" t="n">
-        <v>46124.91666666666</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="2" t="n">
-        <v>46124</v>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>San Jose Earthquakes II</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>Minnesota United II</t>
-        </is>
-      </c>
-      <c r="G317" t="n">
-        <v>0</v>
-      </c>
-      <c r="H317" t="n">
-        <v>0</v>
-      </c>
-      <c r="I317" t="n">
-        <v>0</v>
-      </c>
-      <c r="J317" t="n">
-        <v>0</v>
-      </c>
-      <c r="K317" t="n">
-        <v>0</v>
-      </c>
-      <c r="L317" t="n">
-        <v>0</v>
-      </c>
-      <c r="M317" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N317" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O317" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P317" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
-      <c r="R317" t="n">
-        <v>0</v>
-      </c>
-      <c r="S317" t="n">
-        <v>0</v>
-      </c>
-      <c r="T317" t="n">
-        <v>0</v>
-      </c>
-      <c r="U317" t="n">
-        <v>0</v>
-      </c>
-      <c r="V317" t="n">
-        <v>0</v>
-      </c>
-      <c r="W317" t="n">
-        <v>0</v>
-      </c>
-      <c r="X317" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y317" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY317" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ317" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA317" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB317" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC317" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD317" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE317" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF317" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG317" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH317" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI317" s="3" t="n">
         <v>46124.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-04-12.xlsx
+++ b/jogos_2026-04-12.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Melbourne City FC</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.66</v>
+        <v>2.37</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.06</v>
+        <v>3.2</v>
       </c>
       <c r="R2" t="n">
-        <v>5.38</v>
+        <v>3.1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Melbourne City FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>4.06</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1</v>
+        <v>5.38</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.52</v>
+        <v>3.81</v>
       </c>
       <c r="R95" t="n">
-        <v>4.18</v>
+        <v>3.36</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="Q106" t="n">
         <v>3.48</v>
       </c>
       <c r="R106" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.69</v>
+        <v>5.62</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.48</v>
+        <v>3.81</v>
       </c>
       <c r="R111" t="n">
-        <v>2.81</v>
+        <v>1.74</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF118" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,22 +30500,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q159" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,22 +37789,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,22 +37986,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,22 +39562,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40004,13 +40004,13 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q201" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R201" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S201" t="n">
         <v>0</v>
@@ -40153,22 +40153,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,22 +40744,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42025,10 +42025,10 @@
         <v>0</v>
       </c>
       <c r="AG211" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH211" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q212" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42222,10 +42222,10 @@
         <v>0</v>
       </c>
       <c r="AG212" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH212" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q216" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43010,10 +43010,10 @@
         <v>0</v>
       </c>
       <c r="AG216" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH216" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI216" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43550,13 +43550,13 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q219" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R219" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S219" t="n">
         <v>0</v>
@@ -43601,10 +43601,10 @@
         <v>0</v>
       </c>
       <c r="AG219" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH219" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI219" t="n">
         <v>0</v>
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q220" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43940,7 +43940,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q234" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46698,7 +46698,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P235" t="n">
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,22 +47836,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,22 +48624,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,22 +49215,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,133 +49263,133 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q248" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S248" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T248" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U248" t="n">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="V248" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W248" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X248" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y248" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z248" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA248" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB248" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC248" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD248" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF248" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG248" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AH248" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI248" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="AJ248" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK248" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL248" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AM248" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN248" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AO248" t="n">
         <v>0</v>
       </c>
       <c r="AP248" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR248" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS248" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AT248" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AU248" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV248" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AW248" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AX248" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY248" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ248" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BA248" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB248" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC248" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD248" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE248" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF248" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG248" t="n">
         <v>0</v>
@@ -49412,22 +49412,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,133 +49460,133 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q249" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S249" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T249" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U249" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="V249" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W249" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X249" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y249" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z249" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA249" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB249" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC249" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD249" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE249" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF249" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG249" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH249" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI249" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AJ249" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK249" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL249" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM249" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN249" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO249" t="n">
         <v>0</v>
       </c>
       <c r="AP249" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ249" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR249" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS249" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AU249" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV249" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AW249" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX249" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY249" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ249" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA249" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB249" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC249" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD249" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE249" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF249" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG249" t="n">
         <v>0</v>
@@ -49609,22 +49609,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,22 +50594,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51430,133 +51430,133 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>2.2</v>
+        <v>2.99</v>
       </c>
       <c r="Q259" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="R259" t="n">
-        <v>3.43</v>
+        <v>2.15</v>
       </c>
       <c r="S259" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T259" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U259" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V259" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W259" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X259" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y259" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z259" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA259" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB259" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC259" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD259" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE259" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AF259" t="n">
-        <v>1.89</v>
+        <v>2.27</v>
       </c>
       <c r="AG259" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH259" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI259" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ259" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK259" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL259" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM259" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN259" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO259" t="n">
         <v>0</v>
       </c>
       <c r="AP259" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ259" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR259" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS259" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AT259" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AU259" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AV259" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW259" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX259" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY259" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ259" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA259" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB259" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC259" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BD259" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE259" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF259" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG259" t="n">
         <v>0</v>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51627,13 +51627,13 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q260" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R260" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -51672,10 +51672,10 @@
         <v>0</v>
       </c>
       <c r="AE260" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF260" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG260" t="n">
         <v>0</v>
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,133 +51824,133 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q261" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S261" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T261" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U261" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V261" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W261" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X261" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Y261" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z261" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB261" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC261" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD261" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE261" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF261" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AG261" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH261" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI261" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ261" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK261" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL261" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM261" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN261" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO261" t="n">
         <v>0</v>
       </c>
       <c r="AP261" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR261" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS261" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AT261" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AU261" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AV261" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW261" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX261" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY261" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ261" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA261" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BB261" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC261" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BD261" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE261" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BF261" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG261" t="n">
         <v>0</v>
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,22 +52170,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52218,13 +52218,13 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q263" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S263" t="n">
         <v>0</v>
@@ -52367,7 +52367,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52415,13 +52415,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q264" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R264" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,7 +52761,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53155,22 +53155,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53746,7 +53746,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53794,13 +53794,13 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>1.69</v>
+        <v>3.17</v>
       </c>
       <c r="Q271" t="n">
-        <v>4.16</v>
+        <v>3.58</v>
       </c>
       <c r="R271" t="n">
-        <v>5.43</v>
+        <v>2.38</v>
       </c>
       <c r="S271" t="n">
         <v>0</v>
@@ -53839,10 +53839,10 @@
         <v>0</v>
       </c>
       <c r="AE271" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AF271" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG271" t="n">
         <v>0</v>
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>3.17</v>
+        <v>1.69</v>
       </c>
       <c r="Q272" t="n">
-        <v>3.58</v>
+        <v>4.16</v>
       </c>
       <c r="R272" t="n">
-        <v>2.38</v>
+        <v>5.43</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54036,10 +54036,10 @@
         <v>0</v>
       </c>
       <c r="AE272" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF272" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG272" t="n">
         <v>0</v>
@@ -54140,22 +54140,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,22 +54731,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54928,7 +54928,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -54938,12 +54938,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -55322,22 +55322,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55519,22 +55519,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56908,12 +56908,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58325,13 +58325,13 @@
         </is>
       </c>
       <c r="P294" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q294" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R294" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S294" t="n">
         <v>0</v>
@@ -58474,7 +58474,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58522,13 +58522,13 @@
         </is>
       </c>
       <c r="P295" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q295" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R295" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S295" t="n">
         <v>0</v>
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58719,13 +58719,13 @@
         </is>
       </c>
       <c r="P296" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q296" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R296" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="S296" t="n">
         <v>0</v>
@@ -58764,10 +58764,10 @@
         <v>0</v>
       </c>
       <c r="AE296" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF296" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG296" t="n">
         <v>0</v>
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -58916,13 +58916,13 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>1.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q297" t="n">
-        <v>3.79</v>
+        <v>3.38</v>
       </c>
       <c r="R297" t="n">
-        <v>4.63</v>
+        <v>2.57</v>
       </c>
       <c r="S297" t="n">
         <v>0</v>
@@ -58961,10 +58961,10 @@
         <v>0</v>
       </c>
       <c r="AE297" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF297" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG297" t="n">
         <v>0</v>
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59262,7 +59262,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59310,13 +59310,13 @@
         </is>
       </c>
       <c r="P299" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q299" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R299" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S299" t="n">
         <v>0</v>
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59507,13 +59507,13 @@
         </is>
       </c>
       <c r="P300" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q300" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R300" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="S300" t="n">
         <v>0</v>
@@ -59558,10 +59558,10 @@
         <v>0</v>
       </c>
       <c r="AG300" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH300" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI300" t="n">
         <v>0</v>
@@ -59656,7 +59656,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59704,13 +59704,13 @@
         </is>
       </c>
       <c r="P301" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q301" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="R301" t="n">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="S301" t="n">
         <v>0</v>
@@ -59755,10 +59755,10 @@
         <v>0</v>
       </c>
       <c r="AG301" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH301" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI301" t="n">
         <v>0</v>
@@ -59853,7 +59853,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60247,7 +60247,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -61035,7 +61035,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61232,7 +61232,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61626,7 +61626,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61833,12 +61833,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G312" t="n">

--- a/jogos_2026-04-12.xlsx
+++ b/jogos_2026-04-12.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.52</v>
+        <v>3.81</v>
       </c>
       <c r="R89" t="n">
-        <v>4.18</v>
+        <v>3.36</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.48</v>
+        <v>3.66</v>
       </c>
       <c r="R106" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q165" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,22 +33652,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,22 +36607,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,22 +37789,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,22 +39562,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,22 +39956,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40153,22 +40153,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,22 +40350,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q206" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41034,10 +41034,10 @@
         <v>0</v>
       </c>
       <c r="AE206" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF206" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG206" t="n">
         <v>0</v>
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>3.38</v>
+        <v>2.02</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="R207" t="n">
-        <v>2.33</v>
+        <v>4.68</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF207" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q209" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q212" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42222,10 +42222,10 @@
         <v>0</v>
       </c>
       <c r="AG212" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH212" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI212" t="n">
         <v>0</v>
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>1.54</v>
+        <v>2.98</v>
       </c>
       <c r="Q216" t="n">
-        <v>4.88</v>
+        <v>3.91</v>
       </c>
       <c r="R216" t="n">
-        <v>6.3</v>
+        <v>2.36</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43010,10 +43010,10 @@
         <v>0</v>
       </c>
       <c r="AG216" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH216" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AI216" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43550,13 +43550,13 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q219" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R219" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S219" t="n">
         <v>0</v>
@@ -43601,10 +43601,10 @@
         <v>0</v>
       </c>
       <c r="AG219" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH219" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI219" t="n">
         <v>0</v>
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q220" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43940,7 +43940,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P221" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q234" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46698,7 +46698,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P235" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,22 +47048,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,22 +47836,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,22 +48624,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,22 +49215,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,133 +49460,133 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q249" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S249" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T249" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U249" t="n">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="V249" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W249" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X249" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y249" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z249" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA249" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB249" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC249" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD249" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF249" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG249" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AH249" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI249" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="AJ249" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK249" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL249" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AM249" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN249" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AO249" t="n">
         <v>0</v>
       </c>
       <c r="AP249" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ249" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR249" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS249" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AT249" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AU249" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV249" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AW249" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AX249" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY249" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ249" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BA249" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB249" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC249" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD249" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE249" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF249" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG249" t="n">
         <v>0</v>
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,22 +49806,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50051,133 +50051,133 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q252" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R252" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S252" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T252" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U252" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="V252" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W252" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X252" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y252" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z252" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA252" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB252" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC252" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD252" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE252" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF252" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG252" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH252" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI252" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AJ252" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK252" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL252" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM252" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN252" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO252" t="n">
         <v>0</v>
       </c>
       <c r="AP252" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ252" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR252" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS252" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AT252" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AU252" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV252" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AW252" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX252" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY252" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ252" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA252" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB252" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC252" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD252" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE252" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF252" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG252" t="n">
         <v>0</v>
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,22 +50397,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,22 +50594,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,22 +50988,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51430,133 +51430,133 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>2.99</v>
+        <v>2.2</v>
       </c>
       <c r="Q259" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="R259" t="n">
-        <v>2.15</v>
+        <v>3.43</v>
       </c>
       <c r="S259" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T259" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U259" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V259" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W259" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X259" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Y259" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z259" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA259" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB259" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC259" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD259" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AF259" t="n">
-        <v>2.27</v>
+        <v>1.89</v>
       </c>
       <c r="AG259" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH259" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI259" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ259" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK259" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL259" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM259" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN259" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO259" t="n">
         <v>0</v>
       </c>
       <c r="AP259" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ259" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR259" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS259" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AT259" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AU259" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AV259" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW259" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX259" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY259" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ259" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA259" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BB259" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC259" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BD259" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE259" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BF259" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG259" t="n">
         <v>0</v>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51627,13 +51627,13 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q260" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -51672,10 +51672,10 @@
         <v>0</v>
       </c>
       <c r="AE260" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF260" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG260" t="n">
         <v>0</v>
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,133 +51824,133 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q261" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R261" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S261" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T261" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U261" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V261" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W261" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X261" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y261" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z261" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA261" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB261" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC261" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD261" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE261" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF261" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG261" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH261" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI261" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ261" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK261" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL261" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM261" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN261" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO261" t="n">
         <v>0</v>
       </c>
       <c r="AP261" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ261" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR261" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS261" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AU261" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AV261" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW261" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX261" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY261" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ261" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA261" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB261" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC261" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BD261" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE261" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF261" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG261" t="n">
         <v>0</v>
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,22 +52170,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52218,13 +52218,13 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q263" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R263" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S263" t="n">
         <v>0</v>
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52415,13 +52415,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q264" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -52761,7 +52761,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,7 +52958,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53746,7 +53746,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53794,13 +53794,13 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>3.17</v>
+        <v>1.69</v>
       </c>
       <c r="Q271" t="n">
-        <v>3.58</v>
+        <v>4.16</v>
       </c>
       <c r="R271" t="n">
-        <v>2.38</v>
+        <v>5.43</v>
       </c>
       <c r="S271" t="n">
         <v>0</v>
@@ -53839,10 +53839,10 @@
         <v>0</v>
       </c>
       <c r="AE271" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF271" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG271" t="n">
         <v>0</v>
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>1.69</v>
+        <v>3.17</v>
       </c>
       <c r="Q272" t="n">
-        <v>4.16</v>
+        <v>3.58</v>
       </c>
       <c r="R272" t="n">
-        <v>5.43</v>
+        <v>2.38</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54036,10 +54036,10 @@
         <v>0</v>
       </c>
       <c r="AE272" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AF272" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG272" t="n">
         <v>0</v>
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54928,22 +54928,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -55716,7 +55716,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -56110,7 +56110,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56898,22 +56898,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57686,22 +57686,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -58080,7 +58080,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58128,13 +58128,13 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q293" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R293" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S293" t="n">
         <v>0</v>
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58325,13 +58325,13 @@
         </is>
       </c>
       <c r="P294" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q294" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R294" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S294" t="n">
         <v>0</v>
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58719,13 +58719,13 @@
         </is>
       </c>
       <c r="P296" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q296" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R296" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="S296" t="n">
         <v>0</v>
@@ -58764,10 +58764,10 @@
         <v>0</v>
       </c>
       <c r="AE296" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF296" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG296" t="n">
         <v>0</v>
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59262,7 +59262,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59310,13 +59310,13 @@
         </is>
       </c>
       <c r="P299" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q299" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R299" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="S299" t="n">
         <v>0</v>
@@ -59355,10 +59355,10 @@
         <v>0</v>
       </c>
       <c r="AE299" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF299" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG299" t="n">
         <v>0</v>
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59507,13 +59507,13 @@
         </is>
       </c>
       <c r="P300" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q300" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="R300" t="n">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="S300" t="n">
         <v>0</v>
@@ -59558,10 +59558,10 @@
         <v>0</v>
       </c>
       <c r="AG300" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH300" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI300" t="n">
         <v>0</v>
@@ -59853,7 +59853,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -60050,7 +60050,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60247,7 +60247,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60295,13 +60295,13 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q304" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R304" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="S304" t="n">
         <v>0</v>
@@ -60346,10 +60346,10 @@
         <v>0</v>
       </c>
       <c r="AG304" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH304" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI304" t="n">
         <v>0</v>
@@ -60838,7 +60838,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61035,7 +61035,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61232,7 +61232,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61429,7 +61429,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61626,7 +61626,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61823,7 +61823,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -61833,12 +61833,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G312" t="n">

--- a/jogos_2026-04-12.xlsx
+++ b/jogos_2026-04-12.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Melbourne City FC</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Melbourne City FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,55 +20895,55 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>5.62</v>
+        <v>2.69</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.81</v>
+        <v>3.48</v>
       </c>
       <c r="R104" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF104" t="n">
         <v>1.74</v>
-      </c>
-      <c r="S104" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" t="n">
-        <v>0</v>
-      </c>
-      <c r="V104" t="n">
-        <v>0</v>
-      </c>
-      <c r="W104" t="n">
-        <v>0</v>
-      </c>
-      <c r="X104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF104" t="n">
-        <v>0</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.48</v>
+        <v>3.66</v>
       </c>
       <c r="R109" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF114" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,22 +30500,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q159" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,22 +33652,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,22 +37789,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,22 +38380,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,22 +38971,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,22 +39759,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,22 +39956,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40153,22 +40153,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q206" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R206" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R207" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF207" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>3.38</v>
+        <v>2.02</v>
       </c>
       <c r="Q209" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="R209" t="n">
-        <v>2.33</v>
+        <v>4.68</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41625,10 +41625,10 @@
         <v>0</v>
       </c>
       <c r="AE209" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF209" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG209" t="n">
         <v>0</v>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q211" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42025,10 +42025,10 @@
         <v>0</v>
       </c>
       <c r="AG211" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH211" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>1.54</v>
+        <v>2.98</v>
       </c>
       <c r="Q212" t="n">
-        <v>4.88</v>
+        <v>3.91</v>
       </c>
       <c r="R212" t="n">
-        <v>6.3</v>
+        <v>2.36</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42222,10 +42222,10 @@
         <v>0</v>
       </c>
       <c r="AG212" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH212" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AI212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q216" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43010,10 +43010,10 @@
         <v>0</v>
       </c>
       <c r="AG216" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH216" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI216" t="n">
         <v>0</v>
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q220" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43940,17 +43940,17 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P221" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q221" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R221" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44728,7 +44728,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,22 +47048,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,22 +47836,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,22 +48427,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,133 +49263,133 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q248" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R248" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S248" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T248" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U248" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="V248" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W248" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X248" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y248" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z248" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA248" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB248" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC248" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD248" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE248" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF248" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG248" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH248" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI248" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AJ248" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK248" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL248" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM248" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN248" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO248" t="n">
         <v>0</v>
       </c>
       <c r="AP248" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ248" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR248" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS248" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AU248" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV248" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AW248" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX248" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY248" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ248" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA248" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB248" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC248" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD248" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE248" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF248" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG248" t="n">
         <v>0</v>
@@ -49412,22 +49412,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,22 +49806,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50051,133 +50051,133 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q252" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S252" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T252" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U252" t="n">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="V252" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W252" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X252" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y252" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z252" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB252" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC252" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD252" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF252" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG252" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AH252" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI252" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="AJ252" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK252" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL252" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AM252" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN252" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AO252" t="n">
         <v>0</v>
       </c>
       <c r="AP252" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ252" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR252" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS252" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AT252" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AU252" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV252" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AW252" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AX252" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY252" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ252" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BA252" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB252" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC252" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD252" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE252" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF252" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG252" t="n">
         <v>0</v>
@@ -50200,22 +50200,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,22 +50594,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,22 +50988,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51430,13 +51430,13 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q259" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S259" t="n">
         <v>0</v>
@@ -51475,10 +51475,10 @@
         <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF259" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG259" t="n">
         <v>0</v>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52021,13 +52021,13 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q262" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R262" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S262" t="n">
         <v>0</v>
@@ -52066,10 +52066,10 @@
         <v>0</v>
       </c>
       <c r="AE262" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF262" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG262" t="n">
         <v>0</v>
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52218,13 +52218,13 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q263" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S263" t="n">
         <v>0</v>
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52415,13 +52415,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q264" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R264" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,22 +53352,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53549,22 +53549,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -54140,7 +54140,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -54150,12 +54150,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q273" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55173,13 +55173,13 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q278" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="S278" t="n">
         <v>0</v>
@@ -55322,22 +55322,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55519,22 +55519,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56898,22 +56898,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57292,22 +57292,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -58080,7 +58080,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58128,13 +58128,13 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q293" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R293" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S293" t="n">
         <v>0</v>
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58474,7 +58474,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58522,13 +58522,13 @@
         </is>
       </c>
       <c r="P295" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q295" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R295" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S295" t="n">
         <v>0</v>
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58719,13 +58719,13 @@
         </is>
       </c>
       <c r="P296" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q296" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R296" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S296" t="n">
         <v>0</v>
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -58916,13 +58916,13 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>2.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q297" t="n">
-        <v>3.38</v>
+        <v>3.79</v>
       </c>
       <c r="R297" t="n">
-        <v>2.57</v>
+        <v>4.63</v>
       </c>
       <c r="S297" t="n">
         <v>0</v>
@@ -58961,10 +58961,10 @@
         <v>0</v>
       </c>
       <c r="AE297" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF297" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG297" t="n">
         <v>0</v>
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59262,7 +59262,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59310,13 +59310,13 @@
         </is>
       </c>
       <c r="P299" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q299" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R299" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="S299" t="n">
         <v>0</v>
@@ -59355,10 +59355,10 @@
         <v>0</v>
       </c>
       <c r="AE299" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF299" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG299" t="n">
         <v>0</v>
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59656,7 +59656,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59853,7 +59853,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -59901,13 +59901,13 @@
         </is>
       </c>
       <c r="P302" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q302" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R302" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="S302" t="n">
         <v>0</v>
@@ -59952,10 +59952,10 @@
         <v>0</v>
       </c>
       <c r="AG302" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH302" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI302" t="n">
         <v>0</v>
@@ -60247,7 +60247,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -60257,12 +60257,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -60295,13 +60295,13 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q304" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="R304" t="n">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="S304" t="n">
         <v>0</v>
@@ -60346,10 +60346,10 @@
         <v>0</v>
       </c>
       <c r="AG304" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH304" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI304" t="n">
         <v>0</v>
@@ -60838,7 +60838,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61232,7 +61232,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61429,7 +61429,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61626,7 +61626,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61823,7 +61823,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -61833,12 +61833,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G312" t="n">

--- a/jogos_2026-04-12.xlsx
+++ b/jogos_2026-04-12.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.81</v>
+        <v>2.37</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>4.04</v>
+        <v>3.1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.37</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>4.04</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>7.83</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>13.03</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15036,10 +15036,10 @@
         <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.81</v>
+        <v>3.52</v>
       </c>
       <c r="R88" t="n">
-        <v>3.36</v>
+        <v>4.18</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>5.62</v>
+        <v>2.86</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.81</v>
+        <v>3.66</v>
       </c>
       <c r="R105" t="n">
-        <v>1.74</v>
+        <v>2.55</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.66</v>
+        <v>3.48</v>
       </c>
       <c r="R109" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AF109" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,22 +32667,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,22 +34243,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,22 +37789,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,22 +38380,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,22 +38577,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,22 +38971,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,22 +39562,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q206" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q207" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>2.65</v>
+        <v>2.02</v>
       </c>
       <c r="Q208" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R208" t="n">
-        <v>2.65</v>
+        <v>4.68</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41428,10 +41428,10 @@
         <v>0</v>
       </c>
       <c r="AE208" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF208" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG208" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>2.02</v>
+        <v>2.65</v>
       </c>
       <c r="Q209" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R209" t="n">
-        <v>4.68</v>
+        <v>2.65</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41625,10 +41625,10 @@
         <v>0</v>
       </c>
       <c r="AE209" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF209" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG209" t="n">
         <v>0</v>
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>1.54</v>
+        <v>2.98</v>
       </c>
       <c r="Q211" t="n">
-        <v>4.88</v>
+        <v>3.91</v>
       </c>
       <c r="R211" t="n">
-        <v>6.3</v>
+        <v>2.36</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42025,10 +42025,10 @@
         <v>0</v>
       </c>
       <c r="AG211" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH211" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AI211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42222,10 +42222,10 @@
         <v>0</v>
       </c>
       <c r="AG212" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH212" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q213" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42419,10 +42419,10 @@
         <v>0</v>
       </c>
       <c r="AG213" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH213" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q218" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43743,7 +43743,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43944,13 +43944,13 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q221" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44728,7 +44728,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q234" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48081,13 +48081,13 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q242" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R242" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -48126,10 +48126,10 @@
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF242" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG242" t="n">
         <v>0</v>
@@ -48230,22 +48230,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,22 +48427,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,22 +49215,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,133 +49263,133 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q248" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S248" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T248" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U248" t="n">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="V248" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W248" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X248" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y248" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z248" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA248" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB248" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC248" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD248" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF248" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG248" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AH248" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI248" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="AJ248" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK248" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL248" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AM248" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN248" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AO248" t="n">
         <v>0</v>
       </c>
       <c r="AP248" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR248" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS248" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AT248" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AU248" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV248" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AW248" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AX248" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY248" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ248" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BA248" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB248" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC248" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD248" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE248" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF248" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG248" t="n">
         <v>0</v>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -50003,22 +50003,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,133 +50248,133 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q253" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R253" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S253" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T253" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U253" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="V253" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W253" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X253" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y253" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z253" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA253" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB253" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC253" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD253" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE253" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF253" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG253" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH253" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI253" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AJ253" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK253" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL253" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM253" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN253" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO253" t="n">
         <v>0</v>
       </c>
       <c r="AP253" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ253" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR253" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS253" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AT253" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AU253" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV253" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AW253" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX253" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY253" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ253" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA253" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB253" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC253" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD253" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE253" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF253" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG253" t="n">
         <v>0</v>
@@ -50397,22 +50397,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,22 +50791,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51430,133 +51430,133 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q259" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R259" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S259" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T259" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U259" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V259" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W259" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X259" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y259" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z259" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA259" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB259" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC259" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD259" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE259" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF259" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG259" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH259" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI259" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ259" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK259" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL259" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM259" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN259" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO259" t="n">
         <v>0</v>
       </c>
       <c r="AP259" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ259" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR259" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS259" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AT259" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AU259" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AV259" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW259" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX259" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY259" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ259" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA259" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB259" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC259" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BD259" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE259" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF259" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG259" t="n">
         <v>0</v>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,133 +51824,133 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>2.99</v>
+        <v>2.2</v>
       </c>
       <c r="Q261" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="R261" t="n">
-        <v>2.15</v>
+        <v>3.43</v>
       </c>
       <c r="S261" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T261" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U261" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V261" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W261" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X261" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Y261" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z261" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB261" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC261" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD261" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE261" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AF261" t="n">
-        <v>2.27</v>
+        <v>1.89</v>
       </c>
       <c r="AG261" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH261" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI261" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ261" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK261" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL261" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM261" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN261" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO261" t="n">
         <v>0</v>
       </c>
       <c r="AP261" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR261" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS261" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AT261" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AU261" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AV261" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW261" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX261" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY261" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ261" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA261" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BB261" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC261" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BD261" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE261" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BF261" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG261" t="n">
         <v>0</v>
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52021,13 +52021,13 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q262" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S262" t="n">
         <v>0</v>
@@ -52066,10 +52066,10 @@
         <v>0</v>
       </c>
       <c r="AE262" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF262" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG262" t="n">
         <v>0</v>
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52218,13 +52218,13 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q263" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R263" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S263" t="n">
         <v>0</v>
@@ -52367,7 +52367,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52415,13 +52415,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q264" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53155,22 +53155,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,22 +53352,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53549,22 +53549,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -54140,7 +54140,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -54150,12 +54150,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q273" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54337,7 +54337,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -54347,12 +54347,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54731,22 +54731,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54928,22 +54928,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55173,13 +55173,13 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q278" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R278" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="S278" t="n">
         <v>0</v>
@@ -55322,22 +55322,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55519,22 +55519,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -56307,22 +56307,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56908,12 +56908,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57292,22 +57292,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -57931,13 +57931,13 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q292" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R292" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
@@ -58474,7 +58474,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58522,13 +58522,13 @@
         </is>
       </c>
       <c r="P295" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q295" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R295" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S295" t="n">
         <v>0</v>
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58719,13 +58719,13 @@
         </is>
       </c>
       <c r="P296" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q296" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R296" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S296" t="n">
         <v>0</v>
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -58916,13 +58916,13 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q297" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R297" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="S297" t="n">
         <v>0</v>
@@ -58961,10 +58961,10 @@
         <v>0</v>
       </c>
       <c r="AE297" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF297" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG297" t="n">
         <v>0</v>
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59113,13 +59113,13 @@
         </is>
       </c>
       <c r="P298" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q298" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R298" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="S298" t="n">
         <v>0</v>
@@ -59158,10 +59158,10 @@
         <v>0</v>
       </c>
       <c r="AE298" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF298" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG298" t="n">
         <v>0</v>
@@ -59262,7 +59262,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59310,13 +59310,13 @@
         </is>
       </c>
       <c r="P299" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q299" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R299" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S299" t="n">
         <v>0</v>
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59656,7 +59656,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -60838,7 +60838,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61232,7 +61232,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61429,7 +61429,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61626,7 +61626,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61823,7 +61823,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -61833,12 +61833,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G312" t="n">

--- a/jogos_2026-04-12.xlsx
+++ b/jogos_2026-04-12.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.1</v>
+        <v>2.69</v>
       </c>
       <c r="Q74" t="n">
-        <v>7.83</v>
+        <v>2.75</v>
       </c>
       <c r="R74" t="n">
-        <v>13.03</v>
+        <v>3.21</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15036,10 +15036,10 @@
         <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>7.83</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>13.03</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.48</v>
+        <v>3.66</v>
       </c>
       <c r="R109" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF116" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,22 +32667,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36213,22 +36213,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,22 +38380,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,22 +38971,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,22 +39562,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,22 +39759,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q206" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R206" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>3.38</v>
+        <v>2.02</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="R207" t="n">
-        <v>2.33</v>
+        <v>4.68</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF207" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q208" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R208" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41428,10 +41428,10 @@
         <v>0</v>
       </c>
       <c r="AE208" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF208" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG208" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>2.65</v>
+        <v>3.38</v>
       </c>
       <c r="Q209" t="n">
-        <v>3.1</v>
+        <v>3.46</v>
       </c>
       <c r="R209" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q210" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41828,10 +41828,10 @@
         <v>0</v>
       </c>
       <c r="AG210" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH210" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI210" t="n">
         <v>0</v>
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42025,10 +42025,10 @@
         <v>0</v>
       </c>
       <c r="AG211" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH211" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI211" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="Q213" t="n">
-        <v>4.88</v>
+        <v>4.22</v>
       </c>
       <c r="R213" t="n">
-        <v>6.3</v>
+        <v>4.7</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42419,10 +42419,10 @@
         <v>0</v>
       </c>
       <c r="AG213" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH213" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q214" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42616,10 +42616,10 @@
         <v>0</v>
       </c>
       <c r="AG214" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH214" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI214" t="n">
         <v>0</v>
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q218" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43743,7 +43743,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44334,7 +44334,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P223" t="n">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q234" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46702,13 +46702,13 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q235" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R235" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S235" t="n">
         <v>0</v>
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,22 +47639,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48230,22 +48230,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,13 +49460,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q249" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,22 +49806,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -49854,133 +49854,133 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q251" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R251" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S251" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T251" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U251" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="V251" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W251" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X251" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y251" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z251" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA251" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB251" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC251" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD251" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE251" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF251" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG251" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH251" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI251" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AJ251" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK251" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL251" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM251" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN251" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO251" t="n">
         <v>0</v>
       </c>
       <c r="AP251" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ251" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR251" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS251" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AT251" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AU251" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV251" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AW251" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX251" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY251" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ251" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA251" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB251" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC251" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD251" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE251" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF251" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG251" t="n">
         <v>0</v>
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,133 +50248,133 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q253" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S253" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T253" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U253" t="n">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="V253" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W253" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X253" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y253" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z253" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA253" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB253" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC253" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD253" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF253" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG253" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AH253" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI253" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="AJ253" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK253" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL253" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AM253" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN253" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AO253" t="n">
         <v>0</v>
       </c>
       <c r="AP253" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ253" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR253" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS253" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AT253" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AU253" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV253" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AW253" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AX253" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY253" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ253" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BA253" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB253" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC253" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD253" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE253" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF253" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG253" t="n">
         <v>0</v>
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,22 +50594,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,22 +50988,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52415,13 +52415,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q264" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R264" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53155,22 +53155,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,22 +53352,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53549,22 +53549,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -54337,7 +54337,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -54347,12 +54347,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,7 +54534,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -54544,12 +54544,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,22 +54731,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54928,22 +54928,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -56307,22 +56307,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56898,22 +56898,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -57931,13 +57931,13 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q292" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R292" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58325,13 +58325,13 @@
         </is>
       </c>
       <c r="P294" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q294" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R294" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S294" t="n">
         <v>0</v>
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59113,13 +59113,13 @@
         </is>
       </c>
       <c r="P298" t="n">
-        <v>1.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q298" t="n">
-        <v>3.79</v>
+        <v>3.38</v>
       </c>
       <c r="R298" t="n">
-        <v>4.63</v>
+        <v>2.57</v>
       </c>
       <c r="S298" t="n">
         <v>0</v>
@@ -59158,10 +59158,10 @@
         <v>0</v>
       </c>
       <c r="AE298" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF298" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG298" t="n">
         <v>0</v>
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59310,13 +59310,13 @@
         </is>
       </c>
       <c r="P299" t="n">
-        <v>2.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q299" t="n">
-        <v>3.38</v>
+        <v>3.79</v>
       </c>
       <c r="R299" t="n">
-        <v>2.57</v>
+        <v>4.63</v>
       </c>
       <c r="S299" t="n">
         <v>0</v>
@@ -59355,10 +59355,10 @@
         <v>0</v>
       </c>
       <c r="AE299" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF299" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG299" t="n">
         <v>0</v>
@@ -59656,7 +59656,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -60050,7 +60050,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61035,7 +61035,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61232,7 +61232,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61429,7 +61429,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61626,7 +61626,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61823,7 +61823,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -61833,12 +61833,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G312" t="n">

--- a/jogos_2026-04-12.xlsx
+++ b/jogos_2026-04-12.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Melbourne City FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Melbourne City FC</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.66</v>
+        <v>2.37</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.06</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>5.38</v>
+        <v>3.1</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.75</v>
+        <v>3.32</v>
       </c>
       <c r="R74" t="n">
-        <v>3.21</v>
+        <v>2.66</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>7.83</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>13.03</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15430,10 +15430,10 @@
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>7.83</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>13.03</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.84</v>
+        <v>2.96</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.52</v>
+        <v>4.04</v>
       </c>
       <c r="R91" t="n">
-        <v>4.18</v>
+        <v>2.19</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>5.62</v>
+        <v>2.74</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.81</v>
+        <v>3.48</v>
       </c>
       <c r="R100" t="n">
-        <v>1.74</v>
+        <v>2.75</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.48</v>
+        <v>3.66</v>
       </c>
       <c r="R104" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF119" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>2.79</v>
+        <v>1.6</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.36</v>
+        <v>4.07</v>
       </c>
       <c r="R133" t="n">
-        <v>2.39</v>
+        <v>5.91</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q140" t="n">
-        <v>4.07</v>
+        <v>4.13</v>
       </c>
       <c r="R140" t="n">
-        <v>5.91</v>
+        <v>4.62</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q159" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,22 +34243,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,22 +36016,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,22 +38380,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,22 +38577,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,22 +38971,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>2.02</v>
+        <v>3.38</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="R207" t="n">
-        <v>4.68</v>
+        <v>2.33</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF207" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>3.38</v>
+        <v>2.02</v>
       </c>
       <c r="Q209" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="R209" t="n">
-        <v>2.33</v>
+        <v>4.68</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41625,10 +41625,10 @@
         <v>0</v>
       </c>
       <c r="AE209" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF209" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG209" t="n">
         <v>0</v>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q210" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41828,10 +41828,10 @@
         <v>0</v>
       </c>
       <c r="AG210" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH210" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI210" t="n">
         <v>0</v>
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q212" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42222,10 +42222,10 @@
         <v>0</v>
       </c>
       <c r="AG212" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH212" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="Q213" t="n">
-        <v>4.22</v>
+        <v>4.88</v>
       </c>
       <c r="R213" t="n">
-        <v>4.7</v>
+        <v>6.3</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42419,10 +42419,10 @@
         <v>0</v>
       </c>
       <c r="AG213" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH213" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q214" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42616,10 +42616,10 @@
         <v>0</v>
       </c>
       <c r="AG214" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH214" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI214" t="n">
         <v>0</v>
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q215" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q234" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46702,13 +46702,13 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q235" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S235" t="n">
         <v>0</v>
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q239" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47535,10 +47535,10 @@
         <v>0</v>
       </c>
       <c r="AE239" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF239" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG239" t="n">
         <v>0</v>
@@ -47639,22 +47639,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,22 +48821,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,22 +49215,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,133 +49263,133 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q248" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R248" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S248" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T248" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U248" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="V248" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W248" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X248" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y248" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z248" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA248" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB248" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC248" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD248" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE248" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF248" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG248" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH248" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI248" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AJ248" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK248" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL248" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM248" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN248" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO248" t="n">
         <v>0</v>
       </c>
       <c r="AP248" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ248" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR248" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS248" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AU248" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV248" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AW248" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX248" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY248" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ248" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA248" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB248" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC248" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD248" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE248" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF248" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG248" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -49854,133 +49854,133 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q251" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S251" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T251" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U251" t="n">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="V251" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W251" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X251" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y251" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z251" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA251" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB251" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC251" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD251" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE251" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF251" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG251" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AH251" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI251" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="AJ251" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK251" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL251" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AM251" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN251" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AO251" t="n">
         <v>0</v>
       </c>
       <c r="AP251" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ251" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR251" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS251" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AT251" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AU251" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV251" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AW251" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AX251" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY251" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ251" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BA251" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB251" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC251" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD251" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE251" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF251" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG251" t="n">
         <v>0</v>
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,22 +50397,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,22 +50988,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51430,133 +51430,133 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q259" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S259" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T259" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U259" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V259" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W259" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X259" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Y259" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z259" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA259" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB259" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC259" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD259" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF259" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AG259" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH259" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI259" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ259" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK259" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL259" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM259" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN259" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO259" t="n">
         <v>0</v>
       </c>
       <c r="AP259" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ259" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR259" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS259" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AT259" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AU259" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AV259" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW259" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX259" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY259" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ259" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA259" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BB259" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC259" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BD259" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE259" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BF259" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG259" t="n">
         <v>0</v>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,133 +51824,133 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>2.2</v>
+        <v>2.99</v>
       </c>
       <c r="Q261" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="R261" t="n">
-        <v>3.43</v>
+        <v>2.15</v>
       </c>
       <c r="S261" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T261" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U261" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V261" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W261" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X261" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y261" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z261" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA261" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB261" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC261" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD261" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE261" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AF261" t="n">
-        <v>1.89</v>
+        <v>2.27</v>
       </c>
       <c r="AG261" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH261" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI261" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ261" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK261" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL261" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM261" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN261" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO261" t="n">
         <v>0</v>
       </c>
       <c r="AP261" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ261" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR261" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS261" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AU261" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AV261" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW261" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX261" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY261" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ261" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA261" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB261" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC261" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BD261" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE261" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF261" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG261" t="n">
         <v>0</v>
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52021,13 +52021,13 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q262" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R262" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S262" t="n">
         <v>0</v>
@@ -52066,10 +52066,10 @@
         <v>0</v>
       </c>
       <c r="AE262" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF262" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG262" t="n">
         <v>0</v>
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53155,22 +53155,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,22 +53352,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53549,22 +53549,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53746,7 +53746,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53794,13 +53794,13 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>1.69</v>
+        <v>3.17</v>
       </c>
       <c r="Q271" t="n">
-        <v>4.16</v>
+        <v>3.58</v>
       </c>
       <c r="R271" t="n">
-        <v>5.43</v>
+        <v>2.38</v>
       </c>
       <c r="S271" t="n">
         <v>0</v>
@@ -53839,10 +53839,10 @@
         <v>0</v>
       </c>
       <c r="AE271" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AF271" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG271" t="n">
         <v>0</v>
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>3.17</v>
+        <v>1.69</v>
       </c>
       <c r="Q272" t="n">
-        <v>3.58</v>
+        <v>4.16</v>
       </c>
       <c r="R272" t="n">
-        <v>2.38</v>
+        <v>5.43</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54036,10 +54036,10 @@
         <v>0</v>
       </c>
       <c r="AE272" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF272" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG272" t="n">
         <v>0</v>
@@ -54140,7 +54140,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -54150,12 +54150,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54385,13 +54385,13 @@
         </is>
       </c>
       <c r="P274" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q274" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R274" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="S274" t="n">
         <v>0</v>
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,22 +54731,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54928,22 +54928,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -55135,12 +55135,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55173,13 +55173,13 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q278" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="S278" t="n">
         <v>0</v>
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56898,22 +56898,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57095,22 +57095,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -57931,13 +57931,13 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q292" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R292" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58325,13 +58325,13 @@
         </is>
       </c>
       <c r="P294" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q294" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R294" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S294" t="n">
         <v>0</v>
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58719,13 +58719,13 @@
         </is>
       </c>
       <c r="P296" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q296" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R296" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S296" t="n">
         <v>0</v>
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -58916,13 +58916,13 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q297" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R297" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="S297" t="n">
         <v>0</v>
@@ -58961,10 +58961,10 @@
         <v>0</v>
       </c>
       <c r="AE297" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF297" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG297" t="n">
         <v>0</v>
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59113,13 +59113,13 @@
         </is>
       </c>
       <c r="P298" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q298" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R298" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S298" t="n">
         <v>0</v>
@@ -59262,7 +59262,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59310,13 +59310,13 @@
         </is>
       </c>
       <c r="P299" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q299" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R299" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="S299" t="n">
         <v>0</v>
@@ -59355,10 +59355,10 @@
         <v>0</v>
       </c>
       <c r="AE299" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF299" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG299" t="n">
         <v>0</v>
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59656,7 +59656,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59853,7 +59853,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -59901,13 +59901,13 @@
         </is>
       </c>
       <c r="P302" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q302" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="R302" t="n">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="S302" t="n">
         <v>0</v>
@@ -59952,10 +59952,10 @@
         <v>0</v>
       </c>
       <c r="AG302" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH302" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI302" t="n">
         <v>0</v>
@@ -60050,7 +60050,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -60060,12 +60060,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -60098,13 +60098,13 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q303" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R303" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="S303" t="n">
         <v>0</v>
@@ -60149,10 +60149,10 @@
         <v>0</v>
       </c>
       <c r="AG303" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH303" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI303" t="n">
         <v>0</v>
@@ -60838,7 +60838,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61035,7 +61035,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61232,7 +61232,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61429,7 +61429,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -61626,7 +61626,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -61636,12 +61636,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -61823,7 +61823,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -61833,12 +61833,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G312" t="n">

--- a/jogos_2026-04-12.xlsx
+++ b/jogos_2026-04-12.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Melbourne City FC</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Melbourne City FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.47</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>6.29</v>
+        <v>2.99</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.76</v>
+        <v>3.35</v>
       </c>
       <c r="R42" t="n">
-        <v>3.6</v>
+        <v>4.01</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.86</v>
+        <v>4.74</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="R67" t="n">
-        <v>3.59</v>
+        <v>1.73</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>7.83</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>13.03</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15824,10 +15824,10 @@
         <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.1</v>
+        <v>2.69</v>
       </c>
       <c r="Q82" t="n">
-        <v>7.83</v>
+        <v>2.75</v>
       </c>
       <c r="R82" t="n">
-        <v>13.03</v>
+        <v>3.21</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16612,10 +16612,10 @@
         <v>0</v>
       </c>
       <c r="AG82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="R101" t="n">
-        <v>2.81</v>
+        <v>2.49</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>5.62</v>
+        <v>2.86</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.81</v>
+        <v>3.66</v>
       </c>
       <c r="R110" t="n">
-        <v>1.74</v>
+        <v>2.55</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.49</v>
+        <v>1.53</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.72</v>
+        <v>3.87</v>
       </c>
       <c r="R115" t="n">
-        <v>2.9</v>
+        <v>5.85</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.36</v>
+        <v>2.85</v>
       </c>
       <c r="R125" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,22 +33455,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,22 +37986,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,22 +38380,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,22 +39956,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q204" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>2.65</v>
+        <v>2.14</v>
       </c>
       <c r="Q205" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R205" t="n">
-        <v>2.65</v>
+        <v>3.26</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>2.02</v>
+        <v>3.38</v>
       </c>
       <c r="Q206" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="R206" t="n">
-        <v>4.68</v>
+        <v>2.33</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41034,10 +41034,10 @@
         <v>0</v>
       </c>
       <c r="AE206" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF206" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG206" t="n">
         <v>0</v>
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>3.38</v>
+        <v>2.02</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="R207" t="n">
-        <v>2.33</v>
+        <v>4.68</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF207" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="Q210" t="n">
-        <v>4.22</v>
+        <v>4.88</v>
       </c>
       <c r="R210" t="n">
-        <v>4.7</v>
+        <v>6.3</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41828,10 +41828,10 @@
         <v>0</v>
       </c>
       <c r="AG210" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH210" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI210" t="n">
         <v>0</v>
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q212" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q214" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42616,10 +42616,10 @@
         <v>0</v>
       </c>
       <c r="AG214" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH214" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI214" t="n">
         <v>0</v>
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43944,13 +43944,13 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q221" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R221" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44925,7 +44925,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46107,7 +46107,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,22 +46457,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47293,13 +47293,13 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q238" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R238" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
@@ -47442,22 +47442,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,22 +47639,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,13 +47884,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q241" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R241" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -47929,10 +47929,10 @@
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF241" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG241" t="n">
         <v>0</v>
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48081,13 +48081,13 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q242" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R242" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -48126,10 +48126,10 @@
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF242" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG242" t="n">
         <v>0</v>
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q243" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48323,10 +48323,10 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF243" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG243" t="n">
         <v>0</v>
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q244" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48520,10 +48520,10 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF244" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG244" t="n">
         <v>0</v>
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,22 +49018,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,133 +49066,133 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q247" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R247" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S247" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T247" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U247" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="V247" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W247" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X247" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y247" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z247" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA247" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB247" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC247" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD247" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE247" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF247" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG247" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH247" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI247" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AJ247" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK247" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL247" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM247" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN247" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO247" t="n">
         <v>0</v>
       </c>
       <c r="AP247" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ247" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR247" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS247" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AT247" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AU247" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV247" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AW247" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX247" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY247" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ247" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA247" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB247" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC247" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD247" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE247" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF247" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG247" t="n">
         <v>0</v>
@@ -49215,22 +49215,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,13 +49263,13 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q248" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R248" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S248" t="n">
         <v>0</v>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,13 +49460,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>2.1</v>
+        <v>3.14</v>
       </c>
       <c r="Q249" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="R249" t="n">
-        <v>2.85</v>
+        <v>2.18</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -49505,10 +49505,10 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF249" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG249" t="n">
         <v>0</v>
@@ -49609,22 +49609,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,22 +49806,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50051,133 +50051,133 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q252" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="S252" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T252" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U252" t="n">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="V252" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W252" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X252" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y252" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z252" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB252" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC252" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD252" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF252" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG252" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AH252" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI252" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="AJ252" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK252" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL252" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AM252" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN252" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AO252" t="n">
         <v>0</v>
       </c>
       <c r="AP252" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ252" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR252" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS252" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AT252" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AU252" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV252" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AW252" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AX252" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY252" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ252" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BA252" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB252" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC252" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD252" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE252" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF252" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG252" t="n">
         <v>0</v>
@@ -50200,22 +50200,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,22 +50397,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,22 +50594,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,22 +50791,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q256" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51036,133 +51036,133 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q257" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S257" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T257" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U257" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V257" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W257" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X257" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z257" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA257" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB257" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC257" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD257" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF257" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AG257" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH257" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI257" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ257" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK257" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL257" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM257" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN257" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO257" t="n">
         <v>0</v>
       </c>
       <c r="AP257" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ257" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR257" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS257" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AT257" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AU257" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AV257" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW257" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX257" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY257" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ257" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA257" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BB257" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC257" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BD257" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE257" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BF257" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG257" t="n">
         <v>0</v>
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,133 +51233,133 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q258" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S258" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T258" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U258" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V258" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W258" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X258" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y258" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z258" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA258" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB258" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC258" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD258" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE258" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF258" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG258" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH258" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI258" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ258" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK258" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL258" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM258" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN258" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO258" t="n">
         <v>0</v>
       </c>
       <c r="AP258" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ258" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR258" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS258" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AT258" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AU258" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AV258" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW258" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX258" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY258" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ258" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA258" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB258" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC258" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BD258" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE258" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF258" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG258" t="n">
         <v>0</v>
@@ -51430,13 +51430,13 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q259" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R259" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S259" t="n">
         <v>0</v>
@@ -51973,22 +51973,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52021,13 +52021,13 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>3.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q262" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="R262" t="n">
-        <v>2.23</v>
+        <v>4.6</v>
       </c>
       <c r="S262" t="n">
         <v>0</v>
@@ -52170,22 +52170,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52218,13 +52218,13 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q263" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R263" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S263" t="n">
         <v>0</v>
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53352,7 +53352,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53400,13 +53400,13 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>1.69</v>
+        <v>3.17</v>
       </c>
       <c r="Q269" t="n">
-        <v>4.16</v>
+        <v>3.58</v>
       </c>
       <c r="R269" t="n">
-        <v>5.43</v>
+        <v>2.38</v>
       </c>
       <c r="S269" t="n">
         <v>0</v>
@@ -53445,10 +53445,10 @@
         <v>0</v>
       </c>
       <c r="AE269" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AF269" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG269" t="n">
         <v>0</v>
@@ -53549,7 +53549,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53597,13 +53597,13 @@
         </is>
       </c>
       <c r="P270" t="n">
-        <v>3.17</v>
+        <v>1.69</v>
       </c>
       <c r="Q270" t="n">
-        <v>3.58</v>
+        <v>4.16</v>
       </c>
       <c r="R270" t="n">
-        <v>2.38</v>
+        <v>5.43</v>
       </c>
       <c r="S270" t="n">
         <v>0</v>
@@ -53642,10 +53642,10 @@
         <v>0</v>
       </c>
       <c r="AE270" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF270" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG270" t="n">
         <v>0</v>
@@ -53746,7 +53746,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53943,22 +53943,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q272" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R272" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54140,22 +54140,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q273" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,7 +54534,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -54544,12 +54544,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54731,22 +54731,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54928,22 +54928,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q277" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R277" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55027,10 +55027,10 @@
         <v>0</v>
       </c>
       <c r="AG277" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH277" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI277" t="n">
         <v>0</v>
@@ -55125,22 +55125,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55332,12 +55332,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56504,22 +56504,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q285" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R285" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56908,12 +56908,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57095,22 +57095,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57302,12 +57302,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57489,7 +57489,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -57499,12 +57499,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -57537,13 +57537,13 @@
         </is>
       </c>
       <c r="P290" t="n">
-        <v>3.21</v>
+        <v>1.95</v>
       </c>
       <c r="Q290" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="R290" t="n">
-        <v>2.17</v>
+        <v>4.16</v>
       </c>
       <c r="S290" t="n">
         <v>0</v>
@@ -57582,10 +57582,10 @@
         <v>0</v>
       </c>
       <c r="AE290" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF290" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG290" t="n">
         <v>0</v>
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57883,7 +57883,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -57893,12 +57893,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -57931,13 +57931,13 @@
         </is>
       </c>
       <c r="P292" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q292" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R292" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58128,13 +58128,13 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q293" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R293" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S293" t="n">
         <v>0</v>
@@ -58173,10 +58173,10 @@
         <v>0</v>
       </c>
       <c r="AE293" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF293" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG293" t="n">
         <v>0</v>
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58325,13 +58325,13 @@
         </is>
       </c>
       <c r="P294" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q294" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R294" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="S294" t="n">
         <v>0</v>
@@ -58370,10 +58370,10 @@
         <v>0</v>
       </c>
       <c r="AE294" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF294" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG294" t="n">
         <v>0</v>
@@ -58474,7 +58474,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58522,13 +58522,13 @@
         </is>
       </c>
       <c r="P295" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q295" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R295" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="S295" t="n">
         <v>0</v>
@@ -58567,10 +58567,10 @@
         <v>0</v>
       </c>
       <c r="AE295" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF295" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG295" t="n">
         <v>0</v>
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58719,13 +58719,13 @@
         </is>
       </c>
       <c r="P296" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q296" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R296" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S296" t="n">
         <v>0</v>
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -58916,13 +58916,13 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q297" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R297" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S297" t="n">
         <v>0</v>
@@ -59113,13 +59113,13 @@
         </is>
       </c>
       <c r="P298" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q298" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R298" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="S298" t="n">
         <v>0</v>
@@ -59158,10 +59158,10 @@
         <v>0</v>
       </c>
       <c r="AE298" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF298" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG298" t="n">
         <v>0</v>
@@ -59262,7 +59262,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59656,7 +59656,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -60098,13 +60098,13 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q303" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R303" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S303" t="n">
         <v>0</v>
@@ -60444,7 +60444,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60641,7 +60641,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60838,7 +60838,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61429,7 +61429,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G310" t="n">

--- a/jogos_2026-04-12.xlsx
+++ b/jogos_2026-04-12.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Melbourne City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.13</v>
+        <v>4.06</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9</v>
+        <v>5.38</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Melbourne City FC</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.06</v>
+        <v>3.34</v>
       </c>
       <c r="R8" t="n">
-        <v>5.38</v>
+        <v>4.04</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>1.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>3.84</v>
       </c>
       <c r="R11" t="n">
-        <v>2.99</v>
+        <v>6.29</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.47</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
-        <v>6.29</v>
+        <v>2.99</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.89</v>
+        <v>4.71</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="R49" t="n">
-        <v>3.76</v>
+        <v>1.73</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>4.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="R67" t="n">
-        <v>1.73</v>
+        <v>4.51</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="R75" t="n">
-        <v>2.6</v>
+        <v>3.21</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.1</v>
+        <v>1.78</v>
       </c>
       <c r="Q78" t="n">
-        <v>7.83</v>
+        <v>3.85</v>
       </c>
       <c r="R78" t="n">
-        <v>13.03</v>
+        <v>4.58</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15824,10 +15824,10 @@
         <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>7.83</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>13.03</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16021,10 +16021,10 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.84</v>
+        <v>2.96</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.52</v>
+        <v>4.04</v>
       </c>
       <c r="R87" t="n">
-        <v>4.18</v>
+        <v>2.19</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.96</v>
+        <v>2.08</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.04</v>
+        <v>3.81</v>
       </c>
       <c r="R94" t="n">
-        <v>2.19</v>
+        <v>3.36</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>5.62</v>
+        <v>2.63</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="R99" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.51</v>
+        <v>2.69</v>
       </c>
       <c r="Q100" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="R100" t="n">
-        <v>5.79</v>
+        <v>2.81</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="R101" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.63</v>
+        <v>5.62</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="R104" t="n">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.49</v>
+        <v>3.06</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.72</v>
+        <v>3.51</v>
       </c>
       <c r="R118" t="n">
-        <v>2.9</v>
+        <v>2.16</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF118" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>3.06</v>
+        <v>2.49</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.51</v>
+        <v>3.72</v>
       </c>
       <c r="R119" t="n">
-        <v>2.16</v>
+        <v>2.9</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF119" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.36</v>
+        <v>2.85</v>
       </c>
       <c r="R129" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2.42</v>
+        <v>1.65</v>
       </c>
       <c r="Q130" t="n">
-        <v>3</v>
+        <v>4.13</v>
       </c>
       <c r="R130" t="n">
-        <v>3.03</v>
+        <v>4.62</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="Q139" t="n">
-        <v>4.38</v>
+        <v>3.3</v>
       </c>
       <c r="R139" t="n">
-        <v>6.58</v>
+        <v>4.69</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,22 +28333,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,22 +33849,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,22 +35819,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,22 +36804,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,22 +37789,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,22 +38971,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,22 +39759,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>2.65</v>
+        <v>3.38</v>
       </c>
       <c r="Q204" t="n">
-        <v>3.1</v>
+        <v>3.46</v>
       </c>
       <c r="R204" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>3.38</v>
+        <v>2.02</v>
       </c>
       <c r="Q206" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="R206" t="n">
-        <v>2.33</v>
+        <v>4.68</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41034,10 +41034,10 @@
         <v>0</v>
       </c>
       <c r="AE206" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF206" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG206" t="n">
         <v>0</v>
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>2.02</v>
+        <v>2.65</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R207" t="n">
-        <v>4.68</v>
+        <v>2.65</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF207" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q208" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q210" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41828,10 +41828,10 @@
         <v>0</v>
       </c>
       <c r="AG210" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH210" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI210" t="n">
         <v>0</v>
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q212" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>2.98</v>
+        <v>1.54</v>
       </c>
       <c r="Q213" t="n">
-        <v>3.91</v>
+        <v>4.88</v>
       </c>
       <c r="R213" t="n">
-        <v>2.36</v>
+        <v>6.3</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42419,10 +42419,10 @@
         <v>0</v>
       </c>
       <c r="AG213" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH213" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AI213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q216" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43010,10 +43010,10 @@
         <v>0</v>
       </c>
       <c r="AG216" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH216" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI216" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43747,13 +43747,13 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q220" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -43944,13 +43944,13 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Q221" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44141,13 +44141,13 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q222" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R222" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47293,13 +47293,13 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q238" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R238" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
@@ -47442,22 +47442,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q239" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,13 +47884,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>1.82</v>
+        <v>3.61</v>
       </c>
       <c r="Q241" t="n">
-        <v>3.49</v>
+        <v>3.79</v>
       </c>
       <c r="R241" t="n">
-        <v>4.17</v>
+        <v>2</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -47929,10 +47929,10 @@
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF241" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG241" t="n">
         <v>0</v>
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q243" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48323,10 +48323,10 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF243" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG243" t="n">
         <v>0</v>
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,13 +49263,13 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>2.1</v>
+        <v>3.14</v>
       </c>
       <c r="Q248" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="R248" t="n">
-        <v>2.85</v>
+        <v>2.18</v>
       </c>
       <c r="S248" t="n">
         <v>0</v>
@@ -49308,10 +49308,10 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF248" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG248" t="n">
         <v>0</v>
@@ -49412,22 +49412,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,13 +49460,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q249" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -49505,10 +49505,10 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF249" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG249" t="n">
         <v>0</v>
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,22 +50003,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,13 +50248,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q253" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R253" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51036,133 +51036,133 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q257" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R257" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S257" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T257" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U257" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V257" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W257" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X257" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y257" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z257" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA257" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB257" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC257" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD257" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE257" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF257" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG257" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH257" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI257" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ257" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK257" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL257" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM257" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN257" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO257" t="n">
         <v>0</v>
       </c>
       <c r="AP257" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ257" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR257" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS257" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AT257" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AU257" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AV257" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW257" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX257" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY257" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ257" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA257" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB257" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC257" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BD257" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE257" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF257" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG257" t="n">
         <v>0</v>
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,133 +51233,133 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q258" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S258" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T258" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U258" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V258" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W258" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X258" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Y258" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z258" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA258" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB258" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC258" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD258" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE258" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF258" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AG258" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH258" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI258" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ258" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK258" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL258" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM258" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN258" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO258" t="n">
         <v>0</v>
       </c>
       <c r="AP258" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ258" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR258" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS258" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AT258" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AU258" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AV258" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW258" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX258" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY258" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ258" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA258" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BB258" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC258" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BD258" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE258" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BF258" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG258" t="n">
         <v>0</v>
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51430,13 +51430,13 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="Q259" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="R259" t="n">
-        <v>2.45</v>
+        <v>3.43</v>
       </c>
       <c r="S259" t="n">
         <v>0</v>
@@ -51475,10 +51475,10 @@
         <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF259" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG259" t="n">
         <v>0</v>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51627,13 +51627,13 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="Q260" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="R260" t="n">
-        <v>3.43</v>
+        <v>2.45</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -51672,10 +51672,10 @@
         <v>0</v>
       </c>
       <c r="AE260" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF260" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG260" t="n">
         <v>0</v>
@@ -51973,22 +51973,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52021,13 +52021,13 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>1.77</v>
+        <v>3.24</v>
       </c>
       <c r="Q262" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="R262" t="n">
-        <v>4.6</v>
+        <v>2.23</v>
       </c>
       <c r="S262" t="n">
         <v>0</v>
@@ -52170,22 +52170,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52218,13 +52218,13 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>3.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q263" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="R263" t="n">
-        <v>2.23</v>
+        <v>4.6</v>
       </c>
       <c r="S263" t="n">
         <v>0</v>
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53746,22 +53746,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53794,13 +53794,13 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q271" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R271" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="S271" t="n">
         <v>0</v>
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q272" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54140,22 +54140,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q273" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54928,22 +54928,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q277" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R277" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55027,10 +55027,10 @@
         <v>0</v>
       </c>
       <c r="AG277" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH277" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI277" t="n">
         <v>0</v>
@@ -55125,22 +55125,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55173,13 +55173,13 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q278" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R278" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S278" t="n">
         <v>0</v>
@@ -55224,10 +55224,10 @@
         <v>0</v>
       </c>
       <c r="AG278" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH278" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI278" t="n">
         <v>0</v>
@@ -55332,12 +55332,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55519,7 +55519,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55716,7 +55716,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -55726,12 +55726,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56504,22 +56504,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56552,13 +56552,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q285" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R285" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -56908,12 +56908,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -57292,22 +57292,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57340,13 +57340,13 @@
         </is>
       </c>
       <c r="P289" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q289" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R289" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S289" t="n">
         <v>0</v>
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58325,13 +58325,13 @@
         </is>
       </c>
       <c r="P294" t="n">
-        <v>1.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q294" t="n">
-        <v>3.79</v>
+        <v>3.38</v>
       </c>
       <c r="R294" t="n">
-        <v>4.63</v>
+        <v>2.57</v>
       </c>
       <c r="S294" t="n">
         <v>0</v>
@@ -58370,10 +58370,10 @@
         <v>0</v>
       </c>
       <c r="AE294" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF294" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG294" t="n">
         <v>0</v>
@@ -58474,7 +58474,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58522,13 +58522,13 @@
         </is>
       </c>
       <c r="P295" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q295" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R295" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="S295" t="n">
         <v>0</v>
@@ -58567,10 +58567,10 @@
         <v>0</v>
       </c>
       <c r="AE295" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF295" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG295" t="n">
         <v>0</v>
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -58916,13 +58916,13 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q297" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R297" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S297" t="n">
         <v>0</v>
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59113,13 +59113,13 @@
         </is>
       </c>
       <c r="P298" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q298" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R298" t="n">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="S298" t="n">
         <v>0</v>
@@ -59158,10 +59158,10 @@
         <v>0</v>
       </c>
       <c r="AE298" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF298" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG298" t="n">
         <v>0</v>
@@ -59262,7 +59262,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59507,13 +59507,13 @@
         </is>
       </c>
       <c r="P300" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q300" t="n">
-        <v>4.73</v>
+        <v>3.94</v>
       </c>
       <c r="R300" t="n">
-        <v>5.61</v>
+        <v>5.71</v>
       </c>
       <c r="S300" t="n">
         <v>0</v>
@@ -59552,16 +59552,16 @@
         <v>0</v>
       </c>
       <c r="AE300" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF300" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG300" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH300" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI300" t="n">
         <v>0</v>
@@ -59853,7 +59853,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -59901,13 +59901,13 @@
         </is>
       </c>
       <c r="P302" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q302" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R302" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="S302" t="n">
         <v>0</v>
@@ -59952,10 +59952,10 @@
         <v>0</v>
       </c>
       <c r="AG302" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH302" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI302" t="n">
         <v>0</v>
@@ -60444,7 +60444,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60641,7 +60641,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60838,7 +60838,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61232,7 +61232,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -61429,7 +61429,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -61439,12 +61439,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G310" t="n">

--- a/jogos_2026-04-12.xlsx
+++ b/jogos_2026-04-12.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Melbourne City FC</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.06</v>
+        <v>3.34</v>
       </c>
       <c r="R7" t="n">
-        <v>5.38</v>
+        <v>4.04</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Melbourne City FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.34</v>
+        <v>4.06</v>
       </c>
       <c r="R8" t="n">
-        <v>4.04</v>
+        <v>5.38</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>1.47</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>3.84</v>
       </c>
       <c r="R13" t="n">
-        <v>2.99</v>
+        <v>6.29</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.35</v>
+        <v>3.76</v>
       </c>
       <c r="R40" t="n">
-        <v>4.01</v>
+        <v>3.6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.76</v>
+        <v>3.35</v>
       </c>
       <c r="R41" t="n">
-        <v>3.6</v>
+        <v>4.01</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>4.71</v>
+        <v>1.35</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.62</v>
+        <v>5.39</v>
       </c>
       <c r="R49" t="n">
-        <v>1.73</v>
+        <v>10.9</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.35</v>
+        <v>1.89</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.39</v>
+        <v>3.55</v>
       </c>
       <c r="R56" t="n">
-        <v>10.9</v>
+        <v>3.76</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>7.83</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>13.03</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15036,10 +15036,10 @@
         <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.75</v>
+        <v>3.32</v>
       </c>
       <c r="R75" t="n">
-        <v>3.21</v>
+        <v>2.66</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>7.83</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>13.03</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16021,10 +16021,10 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="R81" t="n">
-        <v>2.21</v>
+        <v>3.21</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="R85" t="n">
-        <v>2.6</v>
+        <v>4.58</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.52</v>
+        <v>3.81</v>
       </c>
       <c r="R91" t="n">
-        <v>4.18</v>
+        <v>3.36</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.63</v>
+        <v>5.62</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="R99" t="n">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.66</v>
+        <v>3.48</v>
       </c>
       <c r="R103" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AF103" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>5.62</v>
+        <v>2.86</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.81</v>
+        <v>3.66</v>
       </c>
       <c r="R104" t="n">
-        <v>1.74</v>
+        <v>2.55</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="Q129" t="n">
-        <v>2.85</v>
+        <v>4.07</v>
       </c>
       <c r="R129" t="n">
-        <v>2.75</v>
+        <v>5.91</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.41</v>
+        <v>2.42</v>
       </c>
       <c r="Q137" t="n">
-        <v>4.38</v>
+        <v>3</v>
       </c>
       <c r="R137" t="n">
-        <v>6.58</v>
+        <v>3.03</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q152" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,22 +33849,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,22 +36804,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q190" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37986,22 +37986,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,22 +38380,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,22 +38577,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,22 +39562,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,22 +39759,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>3.38</v>
+        <v>2.65</v>
       </c>
       <c r="Q204" t="n">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="R204" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>2.14</v>
+        <v>3.38</v>
       </c>
       <c r="Q205" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="R205" t="n">
-        <v>3.26</v>
+        <v>2.33</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>2.65</v>
+        <v>2.14</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R207" t="n">
-        <v>2.65</v>
+        <v>3.26</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q208" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R208" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q210" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q213" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42419,10 +42419,10 @@
         <v>0</v>
       </c>
       <c r="AG213" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH213" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q214" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42616,10 +42616,10 @@
         <v>0</v>
       </c>
       <c r="AG214" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH214" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI214" t="n">
         <v>0</v>
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>2.98</v>
+        <v>1.54</v>
       </c>
       <c r="Q216" t="n">
-        <v>3.91</v>
+        <v>4.88</v>
       </c>
       <c r="R216" t="n">
-        <v>2.36</v>
+        <v>6.3</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43010,10 +43010,10 @@
         <v>0</v>
       </c>
       <c r="AG216" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH216" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AI216" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43550,13 +43550,13 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q219" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R219" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S219" t="n">
         <v>0</v>
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44141,13 +44141,13 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Q222" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R222" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q225" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R225" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q230" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R230" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -45910,7 +45910,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46107,7 +46107,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,13 +47096,13 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q237" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="Q239" t="n">
-        <v>3.88</v>
+        <v>3.49</v>
       </c>
       <c r="R239" t="n">
-        <v>3.72</v>
+        <v>4.17</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47535,10 +47535,10 @@
         <v>0</v>
       </c>
       <c r="AE239" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF239" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG239" t="n">
         <v>0</v>
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47687,13 +47687,13 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q240" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R240" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S240" t="n">
         <v>0</v>
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -47884,13 +47884,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q241" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R241" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -48033,22 +48033,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48081,13 +48081,13 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q242" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -48126,10 +48126,10 @@
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF242" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG242" t="n">
         <v>0</v>
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q243" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48323,10 +48323,10 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF243" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG243" t="n">
         <v>0</v>
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48672,13 +48672,13 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q245" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S245" t="n">
         <v>0</v>
@@ -48717,10 +48717,10 @@
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF245" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG245" t="n">
         <v>0</v>
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,22 +49018,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,133 +49066,133 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="Q247" t="n">
-        <v>4.6</v>
+        <v>3.67</v>
       </c>
       <c r="R247" t="n">
-        <v>5.75</v>
+        <v>2.85</v>
       </c>
       <c r="S247" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T247" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U247" t="n">
-        <v>6.73</v>
+        <v>0</v>
       </c>
       <c r="V247" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W247" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X247" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y247" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z247" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA247" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB247" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC247" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD247" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF247" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG247" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AH247" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI247" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="AJ247" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK247" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL247" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AM247" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN247" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AO247" t="n">
         <v>0</v>
       </c>
       <c r="AP247" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ247" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR247" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS247" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AT247" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AU247" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV247" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AW247" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AX247" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY247" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ247" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BA247" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB247" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC247" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD247" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE247" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF247" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG247" t="n">
         <v>0</v>
@@ -49215,22 +49215,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,13 +49263,13 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q248" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S248" t="n">
         <v>0</v>
@@ -49308,10 +49308,10 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF248" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG248" t="n">
         <v>0</v>
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,13 +49460,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q249" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -49609,22 +49609,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,13 +49657,13 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q250" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S250" t="n">
         <v>0</v>
@@ -49702,10 +49702,10 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF250" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG250" t="n">
         <v>0</v>
@@ -49806,22 +49806,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,22 +50003,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,22 +50200,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50248,133 +50248,133 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="Q253" t="n">
-        <v>3.67</v>
+        <v>4.6</v>
       </c>
       <c r="R253" t="n">
-        <v>2.85</v>
+        <v>5.75</v>
       </c>
       <c r="S253" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T253" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U253" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="V253" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W253" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X253" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y253" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z253" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA253" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB253" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC253" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD253" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE253" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF253" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG253" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH253" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI253" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AJ253" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK253" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL253" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM253" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN253" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO253" t="n">
         <v>0</v>
       </c>
       <c r="AP253" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ253" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR253" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS253" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AT253" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AU253" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV253" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AW253" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX253" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY253" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ253" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA253" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB253" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC253" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD253" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE253" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF253" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG253" t="n">
         <v>0</v>
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,22 +50594,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50642,13 +50642,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q255" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R255" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -50791,22 +50791,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q256" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q258" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51278,10 +51278,10 @@
         <v>0</v>
       </c>
       <c r="AE258" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF258" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG258" t="n">
         <v>0</v>
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51430,13 +51430,13 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="Q259" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="R259" t="n">
-        <v>3.43</v>
+        <v>2.45</v>
       </c>
       <c r="S259" t="n">
         <v>0</v>
@@ -51475,10 +51475,10 @@
         <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF259" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG259" t="n">
         <v>0</v>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51627,13 +51627,13 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q260" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -51776,22 +51776,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,13 +51824,13 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>2.1</v>
+        <v>3.24</v>
       </c>
       <c r="Q261" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="R261" t="n">
-        <v>3.47</v>
+        <v>2.23</v>
       </c>
       <c r="S261" t="n">
         <v>0</v>
@@ -51973,22 +51973,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52021,13 +52021,13 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>3.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q262" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="R262" t="n">
-        <v>2.23</v>
+        <v>4.6</v>
       </c>
       <c r="S262" t="n">
         <v>0</v>
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52218,13 +52218,13 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="Q263" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R263" t="n">
-        <v>4.6</v>
+        <v>3.47</v>
       </c>
       <c r="S263" t="n">
         <v>0</v>
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52958,22 +52958,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53746,22 +53746,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53794,13 +53794,13 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q271" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R271" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="S271" t="n">
         <v>0</v>
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -54140,7 +54140,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -54150,12 +54150,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q273" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54337,22 +54337,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -54534,7 +54534,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -54544,12 +54544,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54582,13 +54582,13 @@
         </is>
       </c>
       <c r="P275" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q275" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R275" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="S275" t="n">
         <v>0</v>
@@ -54731,7 +54731,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -54741,12 +54741,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54779,13 +54779,13 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q276" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R276" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="S276" t="n">
         <v>0</v>
@@ -54928,22 +54928,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -54976,13 +54976,13 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q277" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R277" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -55027,10 +55027,10 @@
         <v>0</v>
       </c>
       <c r="AG277" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH277" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI277" t="n">
         <v>0</v>
@@ -55125,22 +55125,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55173,13 +55173,13 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>1.99</v>
+        <v>7.8</v>
       </c>
       <c r="Q278" t="n">
-        <v>4.1</v>
+        <v>4.86</v>
       </c>
       <c r="R278" t="n">
-        <v>3.38</v>
+        <v>1.43</v>
       </c>
       <c r="S278" t="n">
         <v>0</v>
@@ -55224,10 +55224,10 @@
         <v>0</v>
       </c>
       <c r="AG278" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH278" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI278" t="n">
         <v>0</v>
@@ -55322,7 +55322,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -55332,12 +55332,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55519,7 +55519,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56514,12 +56514,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56898,22 +56898,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -56946,13 +56946,13 @@
         </is>
       </c>
       <c r="P287" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q287" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R287" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S287" t="n">
         <v>0</v>
@@ -57292,22 +57292,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -57340,13 +57340,13 @@
         </is>
       </c>
       <c r="P289" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q289" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R289" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S289" t="n">
         <v>0</v>
@@ -57696,12 +57696,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -57734,13 +57734,13 @@
         </is>
       </c>
       <c r="P291" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q291" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R291" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S291" t="n">
         <v>0</v>
@@ -57779,10 +57779,10 @@
         <v>0</v>
       </c>
       <c r="AE291" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF291" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG291" t="n">
         <v>0</v>
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58128,13 +58128,13 @@
         </is>
       </c>
       <c r="P293" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q293" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R293" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S293" t="n">
         <v>0</v>
@@ -58173,10 +58173,10 @@
         <v>0</v>
       </c>
       <c r="AE293" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF293" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG293" t="n">
         <v>0</v>
@@ -58277,7 +58277,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58325,13 +58325,13 @@
         </is>
       </c>
       <c r="P294" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q294" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R294" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S294" t="n">
         <v>0</v>
@@ -58474,7 +58474,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58522,13 +58522,13 @@
         </is>
       </c>
       <c r="P295" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q295" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R295" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="S295" t="n">
         <v>0</v>
@@ -58567,10 +58567,10 @@
         <v>0</v>
       </c>
       <c r="AE295" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF295" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG295" t="n">
         <v>0</v>
@@ -58671,7 +58671,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -58719,13 +58719,13 @@
         </is>
       </c>
       <c r="P296" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q296" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R296" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="S296" t="n">
         <v>0</v>
@@ -58764,10 +58764,10 @@
         <v>0</v>
       </c>
       <c r="AE296" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF296" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG296" t="n">
         <v>0</v>
@@ -58868,7 +58868,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -58878,12 +58878,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -58916,13 +58916,13 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q297" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R297" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S297" t="n">
         <v>0</v>
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59113,13 +59113,13 @@
         </is>
       </c>
       <c r="P298" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q298" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R298" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="S298" t="n">
         <v>0</v>
@@ -59164,10 +59164,10 @@
         <v>0</v>
       </c>
       <c r="AG298" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH298" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI298" t="n">
         <v>0</v>
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59459,7 +59459,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59507,13 +59507,13 @@
         </is>
       </c>
       <c r="P300" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q300" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R300" t="n">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="S300" t="n">
         <v>0</v>
@@ -59552,10 +59552,10 @@
         <v>0</v>
       </c>
       <c r="AE300" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF300" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG300" t="n">
         <v>0</v>
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -59853,7 +59853,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -59863,12 +59863,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -59901,13 +59901,13 @@
         </is>
       </c>
       <c r="P302" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q302" t="n">
-        <v>4.73</v>
+        <v>3.94</v>
       </c>
       <c r="R302" t="n">
-        <v>5.61</v>
+        <v>5.71</v>
       </c>
       <c r="S302" t="n">
         <v>0</v>
@@ -59946,16 +59946,16 @@
         <v>0</v>
       </c>
       <c r="AE302" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF302" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG302" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH302" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI302" t="n">
         <v>0</v>
@@ -60444,7 +60444,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -60454,12 +60454,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -60641,7 +60641,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -60651,12 +60651,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -60838,7 +60838,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -60848,12 +60848,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -61035,7 +61035,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -61045,12 +61045,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -61242,12 +61242,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G309" t="n">

--- a/jogos_2026-04-12.xlsx
+++ b/jogos_2026-04-12.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.37</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1</v>
+        <v>4.04</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>1.47</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>3.84</v>
       </c>
       <c r="R12" t="n">
-        <v>2.99</v>
+        <v>6.29</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.47</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
-        <v>6.29</v>
+        <v>2.99</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.17</v>
+        <v>4.74</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.42</v>
+        <v>3.87</v>
       </c>
       <c r="R68" t="n">
-        <v>3.16</v>
+        <v>1.73</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>4.74</v>
+        <v>1.86</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.87</v>
+        <v>3.92</v>
       </c>
       <c r="R72" t="n">
-        <v>1.73</v>
+        <v>3.59</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>7.83</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>13.03</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15036,10 +15036,10 @@
         <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.32</v>
+        <v>3.85</v>
       </c>
       <c r="R75" t="n">
-        <v>2.66</v>
+        <v>4.58</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.75</v>
+        <v>3.32</v>
       </c>
       <c r="R81" t="n">
-        <v>3.21</v>
+        <v>2.66</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>7.83</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>13.03</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17006,10 +17006,10 @@
         <v>0</v>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.78</v>
+        <v>2.69</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.85</v>
+        <v>2.75</v>
       </c>
       <c r="R85" t="n">
-        <v>4.58</v>
+        <v>3.21</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>5.62</v>
+        <v>2.63</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="R99" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="R101" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.51</v>
+        <v>2.74</v>
       </c>
       <c r="Q106" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="R106" t="n">
-        <v>5.79</v>
+        <v>2.75</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="R109" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>3.06</v>
+        <v>1.53</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.51</v>
+        <v>3.87</v>
       </c>
       <c r="R113" t="n">
-        <v>2.16</v>
+        <v>5.85</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2.49</v>
+        <v>3.06</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.72</v>
+        <v>3.51</v>
       </c>
       <c r="R119" t="n">
-        <v>2.9</v>
+        <v>2.16</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF119" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="Q124" t="n">
-        <v>4.38</v>
+        <v>4.13</v>
       </c>
       <c r="R124" t="n">
-        <v>6.58</v>
+        <v>4.62</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>3.52</v>
+        <v>1.41</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.2</v>
+        <v>4.38</v>
       </c>
       <c r="R136" t="n">
-        <v>2.09</v>
+        <v>6.58</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.42</v>
+        <v>1.79</v>
       </c>
       <c r="Q137" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R137" t="n">
-        <v>3.03</v>
+        <v>4.69</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.79</v>
+        <v>2.75</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="R139" t="n">
-        <v>4.69</v>
+        <v>2.75</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
      